--- a/data/CotsList.xlsx
+++ b/data/CotsList.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rserghine\Projects React\DsiCenter_Excel\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3EE2BCC-CE92-4B65-8BB8-CECF52AEC0D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC9A910E-9DEC-4A02-AFF6-68D0499B2123}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{67F2D85F-F75B-4B61-9855-239B084B2F7E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{67F2D85F-F75B-4B61-9855-239B084B2F7E}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="688" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="700" uniqueCount="304">
   <si>
     <t>APPLICATION</t>
   </si>
@@ -431,9 +431,6 @@
   </si>
   <si>
     <t>Add user</t>
-  </si>
-  <si>
-    <t>Check User is located in Europe, then Add user</t>
   </si>
   <si>
     <t>now no agreement approval Jonathan DANA, 
@@ -1360,14 +1357,6 @@
   </si>
   <si>
     <t xml:space="preserve">Hello user,
-We provided you the Visual stuidio XXXX license key by mail.
-You can now activate it with your Admin rights.
-Please keep us informed and not cancel the incident.
-Thank you.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hello user,
 You activated the Visual studio XXXX license key with your Admin rights.
 We close the Request.
 Best regards.
@@ -1497,6 +1486,21 @@
 We suggest you to create a new request for another version.
 Best regards</t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Hello user,
+We provided you the Visual studio XXXX license key by mail.
+You can now activate it with your Admin rights.
+Please keep us informed and not cancel the request.
+Thank you.
+</t>
+  </si>
+  <si>
+    <t>Altia Design (13,4_64b) EN</t>
+  </si>
+  <si>
+    <t>Check User is located in Europe, then Add user.
+If version 13 : send by mail : the manual "AltiaAccount-UserGuide.pdf" (in sns.corp\...\Application list\Altia Design 13.4)</t>
   </si>
 </sst>
 </file>
@@ -2456,7 +2460,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="180">
+  <cellXfs count="183">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2523,12 +2527,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2971,6 +2969,21 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3305,7 +3318,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8204D41-40C1-4E72-957A-75C3D992A16F}">
-  <dimension ref="A1:AA966"/>
+  <dimension ref="A1:AA967"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -3323,36 +3336,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="53" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="55" t="s">
+      <c r="B1" s="53" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="55" t="s">
+      <c r="C1" s="53" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="56" t="s">
+      <c r="D1" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="55" t="s">
+      <c r="E1" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="55" t="s">
+      <c r="F1" s="53" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="178" t="s">
+      <c r="G1" s="176" t="s">
+        <v>167</v>
+      </c>
+      <c r="H1" s="177"/>
+      <c r="I1" s="176" t="s">
         <v>168</v>
       </c>
-      <c r="H1" s="179"/>
-      <c r="I1" s="178" t="s">
+      <c r="J1" s="177"/>
+      <c r="K1" s="176" t="s">
         <v>169</v>
       </c>
-      <c r="J1" s="179"/>
-      <c r="K1" s="178" t="s">
-        <v>170</v>
-      </c>
-      <c r="L1" s="179"/>
+      <c r="L1" s="177"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
@@ -3370,28 +3383,28 @@
       <c r="AA1" s="1"/>
     </row>
     <row r="2" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="85"/>
-      <c r="B2" s="85"/>
-      <c r="C2" s="85"/>
-      <c r="D2" s="86"/>
-      <c r="E2" s="85"/>
-      <c r="F2" s="85"/>
-      <c r="G2" s="55" t="s">
+      <c r="A2" s="83"/>
+      <c r="B2" s="83"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="84"/>
+      <c r="E2" s="83"/>
+      <c r="F2" s="83"/>
+      <c r="G2" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="55" t="s">
+      <c r="H2" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="55" t="s">
+      <c r="I2" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="J2" s="55" t="s">
+      <c r="J2" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="K2" s="55" t="s">
+      <c r="K2" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="L2" s="55" t="s">
+      <c r="L2" s="53" t="s">
         <v>7</v>
       </c>
       <c r="M2" s="1"/>
@@ -3411,41 +3424,41 @@
       <c r="AA2" s="1"/>
     </row>
     <row r="3" spans="1:27" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="57" t="s">
+      <c r="A3" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="58" t="s">
+      <c r="B3" s="180" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="58" t="s">
+      <c r="C3" s="181" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="59" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="59" t="s">
+      <c r="D3" s="12" t="s">
+        <v>302</v>
+      </c>
+      <c r="E3" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="60" t="s">
+      <c r="F3" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="60" t="s">
+      <c r="G3" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="H3" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="I3" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="H3" s="60" t="s">
+      <c r="J3" s="13" t="s">
         <v>184</v>
       </c>
-      <c r="I3" s="60" t="s">
+      <c r="K3" s="13" t="s">
         <v>173</v>
       </c>
-      <c r="J3" s="60" t="s">
+      <c r="L3" s="14" t="s">
         <v>185</v>
-      </c>
-      <c r="K3" s="60" t="s">
-        <v>174</v>
-      </c>
-      <c r="L3" s="61" t="s">
-        <v>186</v>
       </c>
       <c r="M3" s="9"/>
       <c r="N3" s="1"/>
@@ -3464,41 +3477,41 @@
       <c r="AA3" s="1"/>
     </row>
     <row r="4" spans="1:27" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="21" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="22" t="s">
+      <c r="A4" s="55" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="180" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="182" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="F4" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4" s="23" t="s">
+      <c r="D4" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="H4" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="I4" s="16" t="s">
         <v>172</v>
       </c>
-      <c r="H4" s="23" t="s">
+      <c r="J4" s="16" t="s">
         <v>184</v>
       </c>
-      <c r="I4" s="23" t="s">
+      <c r="K4" s="16" t="s">
         <v>173</v>
       </c>
-      <c r="J4" s="23" t="s">
+      <c r="L4" s="17" t="s">
         <v>185</v>
-      </c>
-      <c r="K4" s="23" t="s">
-        <v>175</v>
-      </c>
-      <c r="L4" s="24" t="s">
-        <v>187</v>
       </c>
       <c r="M4" s="9"/>
       <c r="N4" s="1"/>
@@ -3517,39 +3530,41 @@
       <c r="AA4" s="1"/>
     </row>
     <row r="5" spans="1:27" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="25"/>
-      <c r="B5" s="19" t="s">
+      <c r="A5" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5" s="20" t="s">
+      <c r="D5" s="37" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="178" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="20" t="s">
+      <c r="G5" s="178" t="s">
+        <v>171</v>
+      </c>
+      <c r="H5" s="178" t="s">
+        <v>183</v>
+      </c>
+      <c r="I5" s="178" t="s">
         <v>172</v>
       </c>
-      <c r="H5" s="20" t="s">
+      <c r="J5" s="178" t="s">
         <v>184</v>
       </c>
-      <c r="I5" s="20" t="s">
-        <v>173</v>
-      </c>
-      <c r="J5" s="20" t="s">
-        <v>185</v>
-      </c>
-      <c r="K5" s="20" t="s">
-        <v>175</v>
-      </c>
-      <c r="L5" s="62" t="s">
-        <v>187</v>
+      <c r="K5" s="178" t="s">
+        <v>174</v>
+      </c>
+      <c r="L5" s="179" t="s">
+        <v>186</v>
       </c>
       <c r="M5" s="9"/>
       <c r="N5" s="1"/>
@@ -3568,7 +3583,7 @@
       <c r="AA5" s="1"/>
     </row>
     <row r="6" spans="1:27" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="25"/>
+      <c r="A6" s="23"/>
       <c r="B6" s="19" t="s">
         <v>16</v>
       </c>
@@ -3576,7 +3591,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>20</v>
@@ -3585,22 +3600,22 @@
         <v>9</v>
       </c>
       <c r="G6" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="H6" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="I6" s="20" t="s">
         <v>172</v>
       </c>
-      <c r="H6" s="20" t="s">
+      <c r="J6" s="20" t="s">
         <v>184</v>
       </c>
-      <c r="I6" s="20" t="s">
-        <v>173</v>
-      </c>
-      <c r="J6" s="20" t="s">
-        <v>185</v>
-      </c>
       <c r="K6" s="20" t="s">
-        <v>175</v>
-      </c>
-      <c r="L6" s="62" t="s">
-        <v>187</v>
+        <v>174</v>
+      </c>
+      <c r="L6" s="60" t="s">
+        <v>186</v>
       </c>
       <c r="M6" s="9"/>
       <c r="N6" s="1"/>
@@ -3619,7 +3634,7 @@
       <c r="AA6" s="1"/>
     </row>
     <row r="7" spans="1:27" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="25"/>
+      <c r="A7" s="23"/>
       <c r="B7" s="19" t="s">
         <v>16</v>
       </c>
@@ -3627,7 +3642,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>20</v>
@@ -3636,22 +3651,22 @@
         <v>9</v>
       </c>
       <c r="G7" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="H7" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="I7" s="20" t="s">
         <v>172</v>
       </c>
-      <c r="H7" s="20" t="s">
+      <c r="J7" s="20" t="s">
         <v>184</v>
       </c>
-      <c r="I7" s="20" t="s">
-        <v>173</v>
-      </c>
-      <c r="J7" s="20" t="s">
-        <v>185</v>
-      </c>
       <c r="K7" s="20" t="s">
-        <v>175</v>
-      </c>
-      <c r="L7" s="62" t="s">
-        <v>187</v>
+        <v>174</v>
+      </c>
+      <c r="L7" s="60" t="s">
+        <v>186</v>
       </c>
       <c r="M7" s="9"/>
       <c r="N7" s="1"/>
@@ -3670,7 +3685,7 @@
       <c r="AA7" s="1"/>
     </row>
     <row r="8" spans="1:27" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="25"/>
+      <c r="A8" s="23"/>
       <c r="B8" s="19" t="s">
         <v>16</v>
       </c>
@@ -3678,7 +3693,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>20</v>
@@ -3687,22 +3702,22 @@
         <v>9</v>
       </c>
       <c r="G8" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="H8" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="I8" s="20" t="s">
         <v>172</v>
       </c>
-      <c r="H8" s="20" t="s">
+      <c r="J8" s="20" t="s">
         <v>184</v>
       </c>
-      <c r="I8" s="20" t="s">
-        <v>173</v>
-      </c>
-      <c r="J8" s="20" t="s">
-        <v>185</v>
-      </c>
       <c r="K8" s="20" t="s">
-        <v>175</v>
-      </c>
-      <c r="L8" s="62" t="s">
-        <v>187</v>
+        <v>174</v>
+      </c>
+      <c r="L8" s="60" t="s">
+        <v>186</v>
       </c>
       <c r="M8" s="9"/>
       <c r="N8" s="1"/>
@@ -3721,39 +3736,39 @@
       <c r="AA8" s="1"/>
     </row>
     <row r="9" spans="1:27" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="26"/>
-      <c r="B9" s="27" t="s">
+      <c r="A9" s="23"/>
+      <c r="B9" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="27" t="s">
+      <c r="C9" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="15" t="s">
-        <v>300</v>
-      </c>
-      <c r="E9" s="15" t="s">
+      <c r="D9" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F9" s="63" t="s">
+      <c r="F9" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="G9" s="63" t="s">
+      <c r="G9" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="H9" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="I9" s="20" t="s">
         <v>172</v>
       </c>
-      <c r="H9" s="63" t="s">
+      <c r="J9" s="20" t="s">
         <v>184</v>
       </c>
-      <c r="I9" s="63" t="s">
-        <v>173</v>
-      </c>
-      <c r="J9" s="63" t="s">
-        <v>185</v>
-      </c>
-      <c r="K9" s="63" t="s">
-        <v>175</v>
-      </c>
-      <c r="L9" s="64" t="s">
-        <v>187</v>
+      <c r="K9" s="20" t="s">
+        <v>174</v>
+      </c>
+      <c r="L9" s="60" t="s">
+        <v>186</v>
       </c>
       <c r="M9" s="9"/>
       <c r="N9" s="1"/>
@@ -3772,24 +3787,40 @@
       <c r="AA9" s="1"/>
     </row>
     <row r="10" spans="1:27" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="48" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10" s="49" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" s="49" t="s">
+      <c r="A10" s="24"/>
+      <c r="B10" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="52"/>
-      <c r="E10" s="52"/>
-      <c r="F10" s="52"/>
-      <c r="G10" s="52"/>
-      <c r="H10" s="52"/>
-      <c r="I10" s="52"/>
-      <c r="J10" s="52"/>
-      <c r="K10" s="52"/>
-      <c r="L10" s="53"/>
+      <c r="D10" s="15" t="s">
+        <v>298</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="F10" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="G10" s="61" t="s">
+        <v>171</v>
+      </c>
+      <c r="H10" s="61" t="s">
+        <v>183</v>
+      </c>
+      <c r="I10" s="61" t="s">
+        <v>172</v>
+      </c>
+      <c r="J10" s="61" t="s">
+        <v>184</v>
+      </c>
+      <c r="K10" s="61" t="s">
+        <v>174</v>
+      </c>
+      <c r="L10" s="62" t="s">
+        <v>186</v>
+      </c>
       <c r="M10" s="9"/>
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
@@ -3807,43 +3838,25 @@
       <c r="AA10" s="1"/>
     </row>
     <row r="11" spans="1:27" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="48" t="s">
-        <v>26</v>
-      </c>
-      <c r="B11" s="49" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" s="49" t="s">
+      <c r="A11" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="47" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="47" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="139" t="s">
-        <v>28</v>
-      </c>
-      <c r="E11" s="140" t="s">
-        <v>29</v>
-      </c>
-      <c r="F11" s="141" t="s">
-        <v>9</v>
-      </c>
-      <c r="G11" s="142" t="s">
-        <v>172</v>
-      </c>
-      <c r="H11" s="143" t="s">
-        <v>184</v>
-      </c>
-      <c r="I11" s="144" t="s">
-        <v>173</v>
-      </c>
-      <c r="J11" s="143" t="s">
-        <v>185</v>
-      </c>
-      <c r="K11" s="144" t="s">
-        <v>175</v>
-      </c>
-      <c r="L11" s="143" t="s">
-        <v>187</v>
-      </c>
-      <c r="M11" s="1"/>
+      <c r="D11" s="50"/>
+      <c r="E11" s="50"/>
+      <c r="F11" s="50"/>
+      <c r="G11" s="50"/>
+      <c r="H11" s="50"/>
+      <c r="I11" s="50"/>
+      <c r="J11" s="50"/>
+      <c r="K11" s="50"/>
+      <c r="L11" s="51"/>
+      <c r="M11" s="9"/>
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
       <c r="P11" s="1"/>
@@ -3860,41 +3873,41 @@
       <c r="AA11" s="1"/>
     </row>
     <row r="12" spans="1:27" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="36" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12" s="37" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" s="37" t="s">
+      <c r="A12" s="46" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="47" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="47" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="69" t="s">
-        <v>33</v>
-      </c>
-      <c r="E12" s="92" t="s">
-        <v>34</v>
-      </c>
-      <c r="F12" s="124" t="s">
-        <v>158</v>
-      </c>
-      <c r="G12" s="105" t="s">
+      <c r="D12" s="137" t="s">
+        <v>28</v>
+      </c>
+      <c r="E12" s="138" t="s">
+        <v>29</v>
+      </c>
+      <c r="F12" s="139" t="s">
+        <v>9</v>
+      </c>
+      <c r="G12" s="140" t="s">
+        <v>171</v>
+      </c>
+      <c r="H12" s="141" t="s">
+        <v>183</v>
+      </c>
+      <c r="I12" s="142" t="s">
         <v>172</v>
       </c>
-      <c r="H12" s="71" t="s">
+      <c r="J12" s="141" t="s">
         <v>184</v>
       </c>
-      <c r="I12" s="70" t="s">
-        <v>173</v>
-      </c>
-      <c r="J12" s="71" t="s">
-        <v>185</v>
-      </c>
-      <c r="K12" s="70" t="s">
-        <v>175</v>
-      </c>
-      <c r="L12" s="71" t="s">
-        <v>187</v>
+      <c r="K12" s="142" t="s">
+        <v>174</v>
+      </c>
+      <c r="L12" s="141" t="s">
+        <v>186</v>
       </c>
       <c r="M12" s="1"/>
       <c r="N12" s="1"/>
@@ -3913,39 +3926,41 @@
       <c r="AA12" s="1"/>
     </row>
     <row r="13" spans="1:27" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="25"/>
-      <c r="B13" s="19" t="s">
+      <c r="A13" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" s="35" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="C13" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="D13" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E13" s="89" t="s">
+      <c r="D13" s="67" t="s">
+        <v>33</v>
+      </c>
+      <c r="E13" s="90" t="s">
         <v>34</v>
       </c>
-      <c r="F13" s="125" t="s">
-        <v>158</v>
-      </c>
-      <c r="G13" s="106" t="s">
+      <c r="F13" s="122" t="s">
+        <v>157</v>
+      </c>
+      <c r="G13" s="103" t="s">
+        <v>171</v>
+      </c>
+      <c r="H13" s="69" t="s">
+        <v>183</v>
+      </c>
+      <c r="I13" s="68" t="s">
         <v>172</v>
       </c>
-      <c r="H13" s="54" t="s">
+      <c r="J13" s="69" t="s">
         <v>184</v>
       </c>
-      <c r="I13" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="J13" s="54" t="s">
-        <v>185</v>
-      </c>
-      <c r="K13" s="11" t="s">
-        <v>175</v>
-      </c>
-      <c r="L13" s="54" t="s">
-        <v>187</v>
+      <c r="K13" s="68" t="s">
+        <v>174</v>
+      </c>
+      <c r="L13" s="69" t="s">
+        <v>186</v>
       </c>
       <c r="M13" s="1"/>
       <c r="N13" s="1"/>
@@ -3964,39 +3979,39 @@
       <c r="AA13" s="1"/>
     </row>
     <row r="14" spans="1:27" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="65"/>
-      <c r="B14" s="66" t="s">
+      <c r="A14" s="23"/>
+      <c r="B14" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="66" t="s">
+      <c r="C14" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="D14" s="34" t="s">
-        <v>36</v>
-      </c>
-      <c r="E14" s="93" t="s">
+      <c r="D14" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E14" s="87" t="s">
         <v>34</v>
       </c>
-      <c r="F14" s="126" t="s">
-        <v>158</v>
-      </c>
-      <c r="G14" s="107" t="s">
+      <c r="F14" s="123" t="s">
+        <v>157</v>
+      </c>
+      <c r="G14" s="104" t="s">
+        <v>171</v>
+      </c>
+      <c r="H14" s="52" t="s">
+        <v>183</v>
+      </c>
+      <c r="I14" s="11" t="s">
         <v>172</v>
       </c>
-      <c r="H14" s="73" t="s">
+      <c r="J14" s="52" t="s">
         <v>184</v>
       </c>
-      <c r="I14" s="72" t="s">
-        <v>173</v>
-      </c>
-      <c r="J14" s="73" t="s">
-        <v>185</v>
-      </c>
-      <c r="K14" s="72" t="s">
-        <v>242</v>
-      </c>
-      <c r="L14" s="73" t="s">
-        <v>240</v>
+      <c r="K14" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="L14" s="52" t="s">
+        <v>186</v>
       </c>
       <c r="M14" s="1"/>
       <c r="N14" s="1"/>
@@ -4015,39 +4030,39 @@
       <c r="AA14" s="1"/>
     </row>
     <row r="15" spans="1:27" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="65"/>
-      <c r="B15" s="66" t="s">
+      <c r="A15" s="63"/>
+      <c r="B15" s="64" t="s">
         <v>32</v>
       </c>
-      <c r="C15" s="66" t="s">
+      <c r="C15" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="D15" s="34" t="s">
-        <v>159</v>
-      </c>
-      <c r="E15" s="93" t="s">
+      <c r="D15" s="32" t="s">
+        <v>36</v>
+      </c>
+      <c r="E15" s="91" t="s">
         <v>34</v>
       </c>
-      <c r="F15" s="126" t="s">
-        <v>158</v>
-      </c>
-      <c r="G15" s="107" t="s">
+      <c r="F15" s="124" t="s">
+        <v>157</v>
+      </c>
+      <c r="G15" s="105" t="s">
+        <v>171</v>
+      </c>
+      <c r="H15" s="71" t="s">
+        <v>183</v>
+      </c>
+      <c r="I15" s="70" t="s">
         <v>172</v>
       </c>
-      <c r="H15" s="73" t="s">
+      <c r="J15" s="71" t="s">
         <v>184</v>
       </c>
-      <c r="I15" s="72" t="s">
-        <v>173</v>
-      </c>
-      <c r="J15" s="73" t="s">
-        <v>185</v>
-      </c>
-      <c r="K15" s="72" t="s">
-        <v>242</v>
-      </c>
-      <c r="L15" s="73" t="s">
-        <v>240</v>
+      <c r="K15" s="70" t="s">
+        <v>241</v>
+      </c>
+      <c r="L15" s="71" t="s">
+        <v>239</v>
       </c>
       <c r="M15" s="1"/>
       <c r="N15" s="1"/>
@@ -4066,24 +4081,40 @@
       <c r="AA15" s="1"/>
     </row>
     <row r="16" spans="1:27" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="74" t="s">
-        <v>148</v>
-      </c>
-      <c r="B16" s="58" t="s">
-        <v>37</v>
-      </c>
-      <c r="C16" s="58" t="s">
+      <c r="A16" s="63"/>
+      <c r="B16" s="64" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="D16" s="67"/>
-      <c r="E16" s="94"/>
-      <c r="F16" s="127"/>
-      <c r="G16" s="108"/>
-      <c r="H16" s="68"/>
-      <c r="I16" s="67"/>
-      <c r="J16" s="68"/>
-      <c r="K16" s="67"/>
-      <c r="L16" s="68"/>
+      <c r="D16" s="32" t="s">
+        <v>158</v>
+      </c>
+      <c r="E16" s="91" t="s">
+        <v>34</v>
+      </c>
+      <c r="F16" s="124" t="s">
+        <v>157</v>
+      </c>
+      <c r="G16" s="105" t="s">
+        <v>171</v>
+      </c>
+      <c r="H16" s="71" t="s">
+        <v>183</v>
+      </c>
+      <c r="I16" s="70" t="s">
+        <v>172</v>
+      </c>
+      <c r="J16" s="71" t="s">
+        <v>184</v>
+      </c>
+      <c r="K16" s="70" t="s">
+        <v>241</v>
+      </c>
+      <c r="L16" s="71" t="s">
+        <v>239</v>
+      </c>
       <c r="M16" s="1"/>
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
@@ -4101,42 +4132,24 @@
       <c r="AA16" s="1"/>
     </row>
     <row r="17" spans="1:27" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="57" t="s">
-        <v>38</v>
-      </c>
-      <c r="B17" s="58" t="s">
-        <v>39</v>
-      </c>
-      <c r="C17" s="58" t="s">
+      <c r="A17" s="72" t="s">
+        <v>147</v>
+      </c>
+      <c r="B17" s="56" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" s="56" t="s">
         <v>8</v>
       </c>
-      <c r="D17" s="59" t="s">
-        <v>40</v>
-      </c>
-      <c r="E17" s="87" t="s">
-        <v>41</v>
-      </c>
-      <c r="F17" s="121" t="s">
-        <v>30</v>
-      </c>
-      <c r="G17" s="103" t="s">
-        <v>172</v>
-      </c>
-      <c r="H17" s="61" t="s">
-        <v>184</v>
-      </c>
-      <c r="I17" s="60" t="s">
-        <v>173</v>
-      </c>
-      <c r="J17" s="61" t="s">
-        <v>185</v>
-      </c>
-      <c r="K17" s="60" t="s">
-        <v>173</v>
-      </c>
-      <c r="L17" s="61" t="s">
-        <v>187</v>
-      </c>
+      <c r="D17" s="65"/>
+      <c r="E17" s="92"/>
+      <c r="F17" s="125"/>
+      <c r="G17" s="106"/>
+      <c r="H17" s="66"/>
+      <c r="I17" s="65"/>
+      <c r="J17" s="66"/>
+      <c r="K17" s="65"/>
+      <c r="L17" s="66"/>
       <c r="M17" s="1"/>
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
@@ -4154,25 +4167,43 @@
       <c r="AA17" s="1"/>
     </row>
     <row r="18" spans="1:27" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="41" t="s">
-        <v>42</v>
-      </c>
-      <c r="B18" s="42" t="s">
-        <v>43</v>
-      </c>
-      <c r="C18" s="42" t="s">
+      <c r="A18" s="55" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="56" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="56" t="s">
         <v>8</v>
       </c>
-      <c r="D18" s="50"/>
-      <c r="E18" s="50"/>
-      <c r="F18" s="50"/>
-      <c r="G18" s="50"/>
-      <c r="H18" s="50"/>
-      <c r="I18" s="50"/>
-      <c r="J18" s="50"/>
-      <c r="K18" s="50"/>
-      <c r="L18" s="51"/>
-      <c r="M18" s="9"/>
+      <c r="D18" s="57" t="s">
+        <v>40</v>
+      </c>
+      <c r="E18" s="85" t="s">
+        <v>41</v>
+      </c>
+      <c r="F18" s="119" t="s">
+        <v>30</v>
+      </c>
+      <c r="G18" s="101" t="s">
+        <v>171</v>
+      </c>
+      <c r="H18" s="59" t="s">
+        <v>183</v>
+      </c>
+      <c r="I18" s="58" t="s">
+        <v>172</v>
+      </c>
+      <c r="J18" s="59" t="s">
+        <v>184</v>
+      </c>
+      <c r="K18" s="58" t="s">
+        <v>172</v>
+      </c>
+      <c r="L18" s="59" t="s">
+        <v>186</v>
+      </c>
+      <c r="M18" s="1"/>
       <c r="N18" s="1"/>
       <c r="O18" s="1"/>
       <c r="P18" s="1"/>
@@ -4189,89 +4220,73 @@
       <c r="AA18" s="1"/>
     </row>
     <row r="19" spans="1:27" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="36" t="s">
+      <c r="A19" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="40" t="s">
+        <v>43</v>
+      </c>
+      <c r="C19" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="48"/>
+      <c r="E19" s="48"/>
+      <c r="F19" s="48"/>
+      <c r="G19" s="48"/>
+      <c r="H19" s="48"/>
+      <c r="I19" s="48"/>
+      <c r="J19" s="48"/>
+      <c r="K19" s="48"/>
+      <c r="L19" s="49"/>
+      <c r="M19" s="9"/>
+      <c r="N19" s="1"/>
+      <c r="O19" s="1"/>
+      <c r="P19" s="1"/>
+      <c r="Q19" s="1"/>
+      <c r="R19" s="1"/>
+      <c r="S19" s="1"/>
+      <c r="T19" s="1"/>
+      <c r="U19" s="1"/>
+      <c r="V19" s="1"/>
+      <c r="W19" s="1"/>
+      <c r="X19" s="1"/>
+      <c r="Y19" s="1"/>
+      <c r="Z19" s="1"/>
+      <c r="AA19" s="1"/>
+    </row>
+    <row r="20" spans="1:27" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="B19" s="37" t="s">
+      <c r="B20" s="35" t="s">
         <v>45</v>
       </c>
-      <c r="C19" s="37" t="s">
+      <c r="C20" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="D19" s="39" t="s">
+      <c r="D20" s="37" t="s">
         <v>46</v>
       </c>
-      <c r="E19" s="163" t="s">
+      <c r="E20" s="161" t="s">
         <v>47</v>
       </c>
-      <c r="F19" s="124" t="s">
+      <c r="F20" s="122" t="s">
         <v>48</v>
       </c>
-      <c r="G19" s="105" t="s">
+      <c r="G20" s="103" t="s">
+        <v>171</v>
+      </c>
+      <c r="H20" s="69" t="s">
+        <v>183</v>
+      </c>
+      <c r="I20" s="68" t="s">
         <v>172</v>
       </c>
-      <c r="H19" s="71" t="s">
+      <c r="J20" s="69" t="s">
         <v>184</v>
       </c>
-      <c r="I19" s="70" t="s">
-        <v>173</v>
-      </c>
-      <c r="J19" s="71" t="s">
-        <v>185</v>
-      </c>
-      <c r="K19" s="70"/>
-      <c r="L19" s="71"/>
-      <c r="M19" s="4"/>
-      <c r="N19" s="4"/>
-      <c r="O19" s="4"/>
-      <c r="P19" s="4"/>
-      <c r="Q19" s="4"/>
-      <c r="R19" s="4"/>
-      <c r="S19" s="4"/>
-      <c r="T19" s="4"/>
-      <c r="U19" s="4"/>
-      <c r="V19" s="4"/>
-      <c r="W19" s="4"/>
-      <c r="X19" s="4"/>
-      <c r="Y19" s="4"/>
-      <c r="Z19" s="4"/>
-      <c r="AA19" s="4"/>
-    </row>
-    <row r="20" spans="1:27" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="25"/>
-      <c r="B20" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="C20" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="D20" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="E20" s="96" t="s">
-        <v>50</v>
-      </c>
-      <c r="F20" s="125" t="s">
-        <v>51</v>
-      </c>
-      <c r="G20" s="106" t="s">
-        <v>172</v>
-      </c>
-      <c r="H20" s="54" t="s">
-        <v>184</v>
-      </c>
-      <c r="I20" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="J20" s="54" t="s">
-        <v>185</v>
-      </c>
-      <c r="K20" s="11" t="s">
-        <v>174</v>
-      </c>
-      <c r="L20" s="54" t="s">
-        <v>186</v>
-      </c>
+      <c r="K20" s="68"/>
+      <c r="L20" s="69"/>
       <c r="M20" s="4"/>
       <c r="N20" s="4"/>
       <c r="O20" s="4"/>
@@ -4289,7 +4304,7 @@
       <c r="AA20" s="4"/>
     </row>
     <row r="21" spans="1:27" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="25"/>
+      <c r="A21" s="23"/>
       <c r="B21" s="19" t="s">
         <v>45</v>
       </c>
@@ -4297,28 +4312,32 @@
         <v>8</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="E21" s="96" t="s">
-        <v>53</v>
-      </c>
-      <c r="F21" s="125" t="s">
-        <v>54</v>
-      </c>
-      <c r="G21" s="106" t="s">
+        <v>49</v>
+      </c>
+      <c r="E21" s="94" t="s">
+        <v>50</v>
+      </c>
+      <c r="F21" s="123" t="s">
+        <v>51</v>
+      </c>
+      <c r="G21" s="104" t="s">
+        <v>171</v>
+      </c>
+      <c r="H21" s="52" t="s">
+        <v>183</v>
+      </c>
+      <c r="I21" s="11" t="s">
         <v>172</v>
       </c>
-      <c r="H21" s="54" t="s">
+      <c r="J21" s="52" t="s">
         <v>184</v>
       </c>
-      <c r="I21" s="11" t="s">
+      <c r="K21" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="J21" s="54" t="s">
+      <c r="L21" s="52" t="s">
         <v>185</v>
       </c>
-      <c r="K21" s="11"/>
-      <c r="L21" s="54"/>
       <c r="M21" s="4"/>
       <c r="N21" s="4"/>
       <c r="O21" s="4"/>
@@ -4336,36 +4355,36 @@
       <c r="AA21" s="4"/>
     </row>
     <row r="22" spans="1:27" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="65"/>
+      <c r="A22" s="23"/>
       <c r="B22" s="19" t="s">
         <v>45</v>
       </c>
       <c r="C22" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="D22" s="148" t="s">
+      <c r="D22" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="E22" s="94" t="s">
+        <v>53</v>
+      </c>
+      <c r="F22" s="123" t="s">
+        <v>54</v>
+      </c>
+      <c r="G22" s="104" t="s">
         <v>171</v>
       </c>
-      <c r="E22" s="96" t="s">
-        <v>167</v>
-      </c>
-      <c r="F22" s="149" t="s">
-        <v>57</v>
-      </c>
-      <c r="G22" s="145" t="s">
+      <c r="H22" s="52" t="s">
+        <v>183</v>
+      </c>
+      <c r="I22" s="11" t="s">
         <v>172</v>
       </c>
-      <c r="H22" s="54" t="s">
+      <c r="J22" s="52" t="s">
         <v>184</v>
       </c>
-      <c r="I22" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="J22" s="54" t="s">
-        <v>185</v>
-      </c>
-      <c r="K22" s="147"/>
-      <c r="L22" s="146"/>
+      <c r="K22" s="11"/>
+      <c r="L22" s="52"/>
       <c r="M22" s="4"/>
       <c r="N22" s="4"/>
       <c r="O22" s="4"/>
@@ -4383,40 +4402,36 @@
       <c r="AA22" s="4"/>
     </row>
     <row r="23" spans="1:27" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="65"/>
-      <c r="B23" s="66" t="s">
+      <c r="A23" s="63"/>
+      <c r="B23" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="C23" s="66" t="s">
+      <c r="C23" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="D23" s="34" t="s">
-        <v>55</v>
-      </c>
-      <c r="E23" s="97" t="s">
-        <v>56</v>
-      </c>
-      <c r="F23" s="150" t="s">
+      <c r="D23" s="146" t="s">
+        <v>170</v>
+      </c>
+      <c r="E23" s="94" t="s">
+        <v>166</v>
+      </c>
+      <c r="F23" s="147" t="s">
         <v>57</v>
       </c>
-      <c r="G23" s="107" t="s">
+      <c r="G23" s="143" t="s">
+        <v>171</v>
+      </c>
+      <c r="H23" s="52" t="s">
+        <v>183</v>
+      </c>
+      <c r="I23" s="11" t="s">
         <v>172</v>
       </c>
-      <c r="H23" s="73" t="s">
+      <c r="J23" s="52" t="s">
         <v>184</v>
       </c>
-      <c r="I23" s="72" t="s">
-        <v>173</v>
-      </c>
-      <c r="J23" s="73" t="s">
-        <v>185</v>
-      </c>
-      <c r="K23" s="72" t="s">
-        <v>174</v>
-      </c>
-      <c r="L23" s="73" t="s">
-        <v>186</v>
-      </c>
+      <c r="K23" s="145"/>
+      <c r="L23" s="144"/>
       <c r="M23" s="4"/>
       <c r="N23" s="4"/>
       <c r="O23" s="4"/>
@@ -4434,59 +4449,75 @@
       <c r="AA23" s="4"/>
     </row>
     <row r="24" spans="1:27" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="41" t="s">
+      <c r="A24" s="63"/>
+      <c r="B24" s="64" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24" s="64" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="E24" s="95" t="s">
+        <v>56</v>
+      </c>
+      <c r="F24" s="148" t="s">
+        <v>57</v>
+      </c>
+      <c r="G24" s="105" t="s">
+        <v>171</v>
+      </c>
+      <c r="H24" s="71" t="s">
+        <v>183</v>
+      </c>
+      <c r="I24" s="70" t="s">
+        <v>172</v>
+      </c>
+      <c r="J24" s="71" t="s">
+        <v>184</v>
+      </c>
+      <c r="K24" s="70" t="s">
+        <v>173</v>
+      </c>
+      <c r="L24" s="71" t="s">
+        <v>185</v>
+      </c>
+      <c r="M24" s="4"/>
+      <c r="N24" s="4"/>
+      <c r="O24" s="4"/>
+      <c r="P24" s="4"/>
+      <c r="Q24" s="4"/>
+      <c r="R24" s="4"/>
+      <c r="S24" s="4"/>
+      <c r="T24" s="4"/>
+      <c r="U24" s="4"/>
+      <c r="V24" s="4"/>
+      <c r="W24" s="4"/>
+      <c r="X24" s="4"/>
+      <c r="Y24" s="4"/>
+      <c r="Z24" s="4"/>
+      <c r="AA24" s="4"/>
+    </row>
+    <row r="25" spans="1:27" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="39" t="s">
         <v>58</v>
       </c>
-      <c r="B24" s="42" t="s">
+      <c r="B25" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="C24" s="42" t="s">
+      <c r="C25" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="D24" s="50"/>
-      <c r="E24" s="98"/>
-      <c r="F24" s="129"/>
-      <c r="G24" s="110"/>
-      <c r="H24" s="51"/>
-      <c r="I24" s="50"/>
-      <c r="J24" s="51"/>
-      <c r="K24" s="50"/>
-      <c r="L24" s="51"/>
-      <c r="M24" s="1"/>
-      <c r="N24" s="1"/>
-      <c r="O24" s="1"/>
-      <c r="P24" s="1"/>
-      <c r="Q24" s="1"/>
-      <c r="R24" s="1"/>
-      <c r="S24" s="1"/>
-      <c r="T24" s="1"/>
-      <c r="U24" s="1"/>
-      <c r="V24" s="1"/>
-      <c r="W24" s="1"/>
-      <c r="X24" s="1"/>
-      <c r="Y24" s="1"/>
-      <c r="Z24" s="1"/>
-      <c r="AA24" s="1"/>
-    </row>
-    <row r="25" spans="1:27" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="57" t="s">
-        <v>60</v>
-      </c>
-      <c r="B25" s="58" t="s">
-        <v>61</v>
-      </c>
-      <c r="C25" s="58" t="s">
-        <v>8</v>
-      </c>
-      <c r="D25" s="67"/>
-      <c r="E25" s="94"/>
+      <c r="D25" s="48"/>
+      <c r="E25" s="96"/>
       <c r="F25" s="127"/>
       <c r="G25" s="108"/>
-      <c r="H25" s="68"/>
-      <c r="I25" s="67"/>
-      <c r="J25" s="68"/>
-      <c r="K25" s="67"/>
-      <c r="L25" s="68"/>
+      <c r="H25" s="49"/>
+      <c r="I25" s="48"/>
+      <c r="J25" s="49"/>
+      <c r="K25" s="48"/>
+      <c r="L25" s="49"/>
       <c r="M25" s="1"/>
       <c r="N25" s="1"/>
       <c r="O25" s="1"/>
@@ -4504,42 +4535,24 @@
       <c r="AA25" s="1"/>
     </row>
     <row r="26" spans="1:27" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="57" t="s">
-        <v>63</v>
-      </c>
-      <c r="B26" s="58" t="s">
-        <v>64</v>
-      </c>
-      <c r="C26" s="58" t="s">
+      <c r="A26" s="55" t="s">
+        <v>60</v>
+      </c>
+      <c r="B26" s="56" t="s">
+        <v>61</v>
+      </c>
+      <c r="C26" s="56" t="s">
         <v>8</v>
       </c>
-      <c r="D26" s="59" t="s">
-        <v>65</v>
-      </c>
-      <c r="E26" s="87" t="s">
-        <v>66</v>
-      </c>
-      <c r="F26" s="121" t="s">
-        <v>67</v>
-      </c>
-      <c r="G26" s="103" t="s">
-        <v>172</v>
-      </c>
-      <c r="H26" s="61" t="s">
-        <v>184</v>
-      </c>
-      <c r="I26" s="60" t="s">
-        <v>173</v>
-      </c>
-      <c r="J26" s="61" t="s">
-        <v>185</v>
-      </c>
-      <c r="K26" s="60" t="s">
-        <v>176</v>
-      </c>
-      <c r="L26" s="61" t="s">
-        <v>188</v>
-      </c>
+      <c r="D26" s="65"/>
+      <c r="E26" s="92"/>
+      <c r="F26" s="125"/>
+      <c r="G26" s="106"/>
+      <c r="H26" s="66"/>
+      <c r="I26" s="65"/>
+      <c r="J26" s="66"/>
+      <c r="K26" s="65"/>
+      <c r="L26" s="66"/>
       <c r="M26" s="1"/>
       <c r="N26" s="1"/>
       <c r="O26" s="1"/>
@@ -4557,40 +4570,40 @@
       <c r="AA26" s="1"/>
     </row>
     <row r="27" spans="1:27" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="57" t="s">
-        <v>68</v>
-      </c>
-      <c r="B27" s="58" t="s">
-        <v>69</v>
-      </c>
-      <c r="C27" s="58" t="s">
+      <c r="A27" s="55" t="s">
+        <v>63</v>
+      </c>
+      <c r="B27" s="56" t="s">
+        <v>64</v>
+      </c>
+      <c r="C27" s="56" t="s">
         <v>8</v>
       </c>
-      <c r="D27" s="80" t="s">
-        <v>70</v>
-      </c>
-      <c r="E27" s="99" t="s">
-        <v>71</v>
-      </c>
-      <c r="F27" s="122" t="s">
-        <v>72</v>
-      </c>
-      <c r="G27" s="111" t="s">
-        <v>177</v>
-      </c>
-      <c r="H27" s="82" t="s">
-        <v>189</v>
-      </c>
-      <c r="I27" s="81" t="s">
-        <v>173</v>
-      </c>
-      <c r="J27" s="82" t="s">
-        <v>185</v>
-      </c>
-      <c r="K27" s="81" t="s">
+      <c r="D27" s="57" t="s">
+        <v>65</v>
+      </c>
+      <c r="E27" s="85" t="s">
+        <v>66</v>
+      </c>
+      <c r="F27" s="119" t="s">
+        <v>67</v>
+      </c>
+      <c r="G27" s="101" t="s">
+        <v>171</v>
+      </c>
+      <c r="H27" s="59" t="s">
+        <v>183</v>
+      </c>
+      <c r="I27" s="58" t="s">
+        <v>172</v>
+      </c>
+      <c r="J27" s="59" t="s">
+        <v>184</v>
+      </c>
+      <c r="K27" s="58" t="s">
         <v>175</v>
       </c>
-      <c r="L27" s="82" t="s">
+      <c r="L27" s="59" t="s">
         <v>187</v>
       </c>
       <c r="M27" s="1"/>
@@ -4610,41 +4623,41 @@
       <c r="AA27" s="1"/>
     </row>
     <row r="28" spans="1:27" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="21" t="s">
-        <v>73</v>
-      </c>
-      <c r="B28" s="22" t="s">
-        <v>74</v>
-      </c>
-      <c r="C28" s="22" t="s">
+      <c r="A28" s="55" t="s">
+        <v>68</v>
+      </c>
+      <c r="B28" s="56" t="s">
+        <v>69</v>
+      </c>
+      <c r="C28" s="56" t="s">
         <v>8</v>
       </c>
-      <c r="D28" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E28" s="95" t="s">
-        <v>76</v>
-      </c>
-      <c r="F28" s="128" t="s">
-        <v>77</v>
+      <c r="D28" s="78" t="s">
+        <v>70</v>
+      </c>
+      <c r="E28" s="97" t="s">
+        <v>71</v>
+      </c>
+      <c r="F28" s="120" t="s">
+        <v>72</v>
       </c>
       <c r="G28" s="109" t="s">
-        <v>178</v>
-      </c>
-      <c r="H28" s="14" t="s">
-        <v>190</v>
-      </c>
-      <c r="I28" s="13" t="s">
-        <v>195</v>
-      </c>
-      <c r="J28" s="14" t="s">
-        <v>198</v>
-      </c>
-      <c r="K28" s="13" t="s">
-        <v>179</v>
-      </c>
-      <c r="L28" s="14" t="s">
-        <v>191</v>
+        <v>176</v>
+      </c>
+      <c r="H28" s="80" t="s">
+        <v>188</v>
+      </c>
+      <c r="I28" s="79" t="s">
+        <v>172</v>
+      </c>
+      <c r="J28" s="80" t="s">
+        <v>184</v>
+      </c>
+      <c r="K28" s="79" t="s">
+        <v>174</v>
+      </c>
+      <c r="L28" s="80" t="s">
+        <v>186</v>
       </c>
       <c r="M28" s="1"/>
       <c r="N28" s="1"/>
@@ -4663,39 +4676,41 @@
       <c r="AA28" s="1"/>
     </row>
     <row r="29" spans="1:27" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="65"/>
-      <c r="B29" s="66" t="s">
+      <c r="A29" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="B29" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="C29" s="66" t="s">
+      <c r="C29" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="D29" s="34" t="s">
-        <v>78</v>
-      </c>
-      <c r="E29" s="97" t="s">
+      <c r="D29" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E29" s="93" t="s">
         <v>76</v>
       </c>
       <c r="F29" s="126" t="s">
         <v>77</v>
       </c>
       <c r="G29" s="107" t="s">
+        <v>177</v>
+      </c>
+      <c r="H29" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="I29" s="13" t="s">
+        <v>194</v>
+      </c>
+      <c r="J29" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="K29" s="13" t="s">
         <v>178</v>
       </c>
-      <c r="H29" s="73" t="s">
+      <c r="L29" s="14" t="s">
         <v>190</v>
-      </c>
-      <c r="I29" s="72" t="s">
-        <v>195</v>
-      </c>
-      <c r="J29" s="73" t="s">
-        <v>198</v>
-      </c>
-      <c r="K29" s="72" t="s">
-        <v>179</v>
-      </c>
-      <c r="L29" s="73" t="s">
-        <v>191</v>
       </c>
       <c r="M29" s="1"/>
       <c r="N29" s="1"/>
@@ -4714,39 +4729,39 @@
       <c r="AA29" s="1"/>
     </row>
     <row r="30" spans="1:27" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="65"/>
-      <c r="B30" s="66" t="s">
+      <c r="A30" s="63"/>
+      <c r="B30" s="64" t="s">
         <v>74</v>
       </c>
-      <c r="C30" s="66" t="s">
+      <c r="C30" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="D30" s="34" t="s">
-        <v>239</v>
-      </c>
-      <c r="E30" s="97" t="s">
+      <c r="D30" s="32" t="s">
+        <v>78</v>
+      </c>
+      <c r="E30" s="95" t="s">
         <v>76</v>
       </c>
-      <c r="F30" s="126" t="s">
+      <c r="F30" s="124" t="s">
         <v>77</v>
       </c>
-      <c r="G30" s="107" t="s">
+      <c r="G30" s="105" t="s">
+        <v>177</v>
+      </c>
+      <c r="H30" s="71" t="s">
+        <v>189</v>
+      </c>
+      <c r="I30" s="70" t="s">
+        <v>194</v>
+      </c>
+      <c r="J30" s="71" t="s">
+        <v>197</v>
+      </c>
+      <c r="K30" s="70" t="s">
         <v>178</v>
       </c>
-      <c r="H30" s="73" t="s">
+      <c r="L30" s="71" t="s">
         <v>190</v>
-      </c>
-      <c r="I30" s="72" t="s">
-        <v>195</v>
-      </c>
-      <c r="J30" s="73" t="s">
-        <v>198</v>
-      </c>
-      <c r="K30" s="72" t="s">
-        <v>179</v>
-      </c>
-      <c r="L30" s="73" t="s">
-        <v>191</v>
       </c>
       <c r="M30" s="1"/>
       <c r="N30" s="1"/>
@@ -4765,41 +4780,39 @@
       <c r="AA30" s="1"/>
     </row>
     <row r="31" spans="1:27" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="21" t="s">
-        <v>79</v>
-      </c>
-      <c r="B31" s="22" t="s">
-        <v>80</v>
-      </c>
-      <c r="C31" s="22" t="s">
+      <c r="A31" s="63"/>
+      <c r="B31" s="64" t="s">
+        <v>74</v>
+      </c>
+      <c r="C31" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="D31" s="12" t="s">
-        <v>162</v>
-      </c>
-      <c r="E31" s="88" t="s">
-        <v>82</v>
-      </c>
-      <c r="F31" s="128" t="s">
-        <v>83</v>
-      </c>
-      <c r="G31" s="109" t="s">
-        <v>172</v>
-      </c>
-      <c r="H31" s="14" t="s">
-        <v>184</v>
-      </c>
-      <c r="I31" s="13" t="s">
-        <v>172</v>
-      </c>
-      <c r="J31" s="14" t="s">
-        <v>184</v>
-      </c>
-      <c r="K31" s="13" t="s">
-        <v>180</v>
-      </c>
-      <c r="L31" s="14" t="s">
-        <v>192</v>
+      <c r="D31" s="32" t="s">
+        <v>238</v>
+      </c>
+      <c r="E31" s="95" t="s">
+        <v>76</v>
+      </c>
+      <c r="F31" s="124" t="s">
+        <v>77</v>
+      </c>
+      <c r="G31" s="105" t="s">
+        <v>177</v>
+      </c>
+      <c r="H31" s="71" t="s">
+        <v>189</v>
+      </c>
+      <c r="I31" s="70" t="s">
+        <v>194</v>
+      </c>
+      <c r="J31" s="71" t="s">
+        <v>197</v>
+      </c>
+      <c r="K31" s="70" t="s">
+        <v>178</v>
+      </c>
+      <c r="L31" s="71" t="s">
+        <v>190</v>
       </c>
       <c r="M31" s="1"/>
       <c r="N31" s="1"/>
@@ -4818,39 +4831,41 @@
       <c r="AA31" s="1"/>
     </row>
     <row r="32" spans="1:27" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="83"/>
-      <c r="B32" s="27" t="s">
+      <c r="A32" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="B32" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="C32" s="27" t="s">
+      <c r="C32" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="D32" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="E32" s="90" t="s">
+      <c r="D32" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="E32" s="86" t="s">
         <v>82</v>
       </c>
-      <c r="F32" s="130" t="s">
+      <c r="F32" s="126" t="s">
         <v>83</v>
       </c>
-      <c r="G32" s="112" t="s">
-        <v>181</v>
-      </c>
-      <c r="H32" s="17" t="s">
-        <v>193</v>
-      </c>
-      <c r="I32" s="16" t="s">
-        <v>173</v>
-      </c>
-      <c r="J32" s="17" t="s">
-        <v>185</v>
-      </c>
-      <c r="K32" s="16" t="s">
-        <v>182</v>
-      </c>
-      <c r="L32" s="17" t="s">
-        <v>194</v>
+      <c r="G32" s="107" t="s">
+        <v>171</v>
+      </c>
+      <c r="H32" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="I32" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="J32" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="K32" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="L32" s="14" t="s">
+        <v>191</v>
       </c>
       <c r="M32" s="1"/>
       <c r="N32" s="1"/>
@@ -4869,24 +4884,40 @@
       <c r="AA32" s="1"/>
     </row>
     <row r="33" spans="1:27" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="39" t="s">
-        <v>84</v>
-      </c>
-      <c r="B33" s="37" t="s">
-        <v>85</v>
-      </c>
-      <c r="C33" s="37" t="s">
+      <c r="A33" s="81"/>
+      <c r="B33" s="25" t="s">
+        <v>80</v>
+      </c>
+      <c r="C33" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D33" s="78"/>
-      <c r="E33" s="100"/>
-      <c r="F33" s="131"/>
-      <c r="G33" s="113"/>
-      <c r="H33" s="78"/>
-      <c r="I33" s="78"/>
-      <c r="J33" s="78"/>
-      <c r="K33" s="78"/>
-      <c r="L33" s="78"/>
+      <c r="D33" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="E33" s="88" t="s">
+        <v>82</v>
+      </c>
+      <c r="F33" s="128" t="s">
+        <v>83</v>
+      </c>
+      <c r="G33" s="110" t="s">
+        <v>180</v>
+      </c>
+      <c r="H33" s="17" t="s">
+        <v>192</v>
+      </c>
+      <c r="I33" s="16" t="s">
+        <v>172</v>
+      </c>
+      <c r="J33" s="17" t="s">
+        <v>184</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>181</v>
+      </c>
+      <c r="L33" s="17" t="s">
+        <v>193</v>
+      </c>
       <c r="M33" s="1"/>
       <c r="N33" s="1"/>
       <c r="O33" s="1"/>
@@ -4904,24 +4935,24 @@
       <c r="AA33" s="1"/>
     </row>
     <row r="34" spans="1:27" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="34" t="s">
-        <v>86</v>
-      </c>
-      <c r="B34" s="66" t="s">
-        <v>87</v>
-      </c>
-      <c r="C34" s="66" t="s">
+      <c r="A34" s="37" t="s">
+        <v>84</v>
+      </c>
+      <c r="B34" s="35" t="s">
+        <v>85</v>
+      </c>
+      <c r="C34" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="D34" s="75"/>
-      <c r="E34" s="101"/>
-      <c r="F34" s="132"/>
-      <c r="G34" s="114"/>
-      <c r="H34" s="75"/>
-      <c r="I34" s="75"/>
-      <c r="J34" s="75"/>
-      <c r="K34" s="75"/>
-      <c r="L34" s="75"/>
+      <c r="D34" s="76"/>
+      <c r="E34" s="98"/>
+      <c r="F34" s="129"/>
+      <c r="G34" s="111"/>
+      <c r="H34" s="76"/>
+      <c r="I34" s="76"/>
+      <c r="J34" s="76"/>
+      <c r="K34" s="76"/>
+      <c r="L34" s="76"/>
       <c r="M34" s="1"/>
       <c r="N34" s="1"/>
       <c r="O34" s="1"/>
@@ -4939,42 +4970,24 @@
       <c r="AA34" s="1"/>
     </row>
     <row r="35" spans="1:27" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="21" t="s">
-        <v>88</v>
-      </c>
-      <c r="B35" s="22" t="s">
-        <v>89</v>
-      </c>
-      <c r="C35" s="22" t="s">
+      <c r="A35" s="32" t="s">
+        <v>86</v>
+      </c>
+      <c r="B35" s="64" t="s">
+        <v>87</v>
+      </c>
+      <c r="C35" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="D35" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="E35" s="88" t="s">
-        <v>91</v>
-      </c>
-      <c r="F35" s="128" t="s">
-        <v>92</v>
-      </c>
-      <c r="G35" s="109" t="s">
-        <v>181</v>
-      </c>
-      <c r="H35" s="14" t="s">
-        <v>193</v>
-      </c>
-      <c r="I35" s="13" t="s">
-        <v>173</v>
-      </c>
-      <c r="J35" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="K35" s="13" t="s">
-        <v>182</v>
-      </c>
-      <c r="L35" s="14" t="s">
-        <v>194</v>
-      </c>
+      <c r="D35" s="73"/>
+      <c r="E35" s="99"/>
+      <c r="F35" s="130"/>
+      <c r="G35" s="112"/>
+      <c r="H35" s="73"/>
+      <c r="I35" s="73"/>
+      <c r="J35" s="73"/>
+      <c r="K35" s="73"/>
+      <c r="L35" s="73"/>
       <c r="M35" s="1"/>
       <c r="N35" s="1"/>
       <c r="O35" s="1"/>
@@ -4992,39 +5005,41 @@
       <c r="AA35" s="1"/>
     </row>
     <row r="36" spans="1:27" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="25"/>
-      <c r="B36" s="19" t="s">
+      <c r="A36" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="B36" s="22" t="s">
         <v>89</v>
       </c>
-      <c r="C36" s="19" t="s">
+      <c r="C36" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="D36" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="E36" s="89" t="s">
+      <c r="D36" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="E36" s="86" t="s">
         <v>91</v>
       </c>
-      <c r="F36" s="125" t="s">
+      <c r="F36" s="126" t="s">
         <v>92</v>
       </c>
-      <c r="G36" s="106" t="s">
+      <c r="G36" s="107" t="s">
+        <v>180</v>
+      </c>
+      <c r="H36" s="14" t="s">
+        <v>192</v>
+      </c>
+      <c r="I36" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="J36" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="K36" s="13" t="s">
         <v>181</v>
       </c>
-      <c r="H36" s="54" t="s">
+      <c r="L36" s="14" t="s">
         <v>193</v>
-      </c>
-      <c r="I36" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="J36" s="54" t="s">
-        <v>185</v>
-      </c>
-      <c r="K36" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="L36" s="54" t="s">
-        <v>194</v>
       </c>
       <c r="M36" s="1"/>
       <c r="N36" s="1"/>
@@ -5043,39 +5058,39 @@
       <c r="AA36" s="1"/>
     </row>
     <row r="37" spans="1:27" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="26"/>
-      <c r="B37" s="27" t="s">
+      <c r="A37" s="23"/>
+      <c r="B37" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="C37" s="27" t="s">
+      <c r="C37" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="D37" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="E37" s="90" t="s">
+      <c r="D37" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="E37" s="87" t="s">
         <v>91</v>
       </c>
-      <c r="F37" s="130" t="s">
+      <c r="F37" s="123" t="s">
         <v>92</v>
       </c>
-      <c r="G37" s="112" t="s">
+      <c r="G37" s="104" t="s">
+        <v>180</v>
+      </c>
+      <c r="H37" s="52" t="s">
+        <v>192</v>
+      </c>
+      <c r="I37" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="J37" s="52" t="s">
+        <v>184</v>
+      </c>
+      <c r="K37" s="11" t="s">
         <v>181</v>
       </c>
-      <c r="H37" s="17" t="s">
+      <c r="L37" s="52" t="s">
         <v>193</v>
-      </c>
-      <c r="I37" s="16" t="s">
-        <v>173</v>
-      </c>
-      <c r="J37" s="17" t="s">
-        <v>185</v>
-      </c>
-      <c r="K37" s="16" t="s">
-        <v>182</v>
-      </c>
-      <c r="L37" s="17" t="s">
-        <v>194</v>
       </c>
       <c r="M37" s="1"/>
       <c r="N37" s="1"/>
@@ -5094,41 +5109,39 @@
       <c r="AA37" s="1"/>
     </row>
     <row r="38" spans="1:27" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="36" t="s">
-        <v>95</v>
-      </c>
-      <c r="B38" s="37" t="s">
-        <v>96</v>
-      </c>
-      <c r="C38" s="37" t="s">
+      <c r="A38" s="24"/>
+      <c r="B38" s="25" t="s">
+        <v>89</v>
+      </c>
+      <c r="C38" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D38" s="84" t="s">
-        <v>97</v>
-      </c>
-      <c r="E38" s="92" t="s">
-        <v>98</v>
-      </c>
-      <c r="F38" s="124" t="s">
-        <v>200</v>
-      </c>
-      <c r="G38" s="105" t="s">
+      <c r="D38" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="E38" s="88" t="s">
+        <v>91</v>
+      </c>
+      <c r="F38" s="128" t="s">
+        <v>92</v>
+      </c>
+      <c r="G38" s="110" t="s">
+        <v>180</v>
+      </c>
+      <c r="H38" s="17" t="s">
+        <v>192</v>
+      </c>
+      <c r="I38" s="16" t="s">
         <v>172</v>
       </c>
-      <c r="H38" s="71" t="s">
+      <c r="J38" s="17" t="s">
         <v>184</v>
       </c>
-      <c r="I38" s="70" t="s">
-        <v>173</v>
-      </c>
-      <c r="J38" s="71" t="s">
-        <v>185</v>
-      </c>
-      <c r="K38" s="70" t="s">
-        <v>175</v>
-      </c>
-      <c r="L38" s="71" t="s">
-        <v>187</v>
+      <c r="K38" s="16" t="s">
+        <v>181</v>
+      </c>
+      <c r="L38" s="17" t="s">
+        <v>193</v>
       </c>
       <c r="M38" s="1"/>
       <c r="N38" s="1"/>
@@ -5147,39 +5160,41 @@
       <c r="AA38" s="1"/>
     </row>
     <row r="39" spans="1:27" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="25"/>
-      <c r="B39" s="19" t="s">
+      <c r="A39" s="34" t="s">
+        <v>95</v>
+      </c>
+      <c r="B39" s="35" t="s">
         <v>96</v>
       </c>
-      <c r="C39" s="19" t="s">
+      <c r="C39" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="D39" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="E39" s="89" t="s">
+      <c r="D39" s="82" t="s">
+        <v>97</v>
+      </c>
+      <c r="E39" s="90" t="s">
         <v>98</v>
       </c>
-      <c r="F39" s="125" t="s">
-        <v>200</v>
-      </c>
-      <c r="G39" s="106" t="s">
+      <c r="F39" s="122" t="s">
+        <v>199</v>
+      </c>
+      <c r="G39" s="103" t="s">
+        <v>171</v>
+      </c>
+      <c r="H39" s="69" t="s">
+        <v>183</v>
+      </c>
+      <c r="I39" s="68" t="s">
         <v>172</v>
       </c>
-      <c r="H39" s="54" t="s">
+      <c r="J39" s="69" t="s">
         <v>184</v>
       </c>
-      <c r="I39" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="J39" s="54" t="s">
-        <v>185</v>
-      </c>
-      <c r="K39" s="11" t="s">
-        <v>175</v>
-      </c>
-      <c r="L39" s="54" t="s">
-        <v>187</v>
+      <c r="K39" s="68" t="s">
+        <v>174</v>
+      </c>
+      <c r="L39" s="69" t="s">
+        <v>186</v>
       </c>
       <c r="M39" s="1"/>
       <c r="N39" s="1"/>
@@ -5198,39 +5213,39 @@
       <c r="AA39" s="1"/>
     </row>
     <row r="40" spans="1:27" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="26"/>
-      <c r="B40" s="27" t="s">
+      <c r="A40" s="23"/>
+      <c r="B40" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="C40" s="27" t="s">
+      <c r="C40" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="D40" s="76" t="s">
-        <v>100</v>
-      </c>
-      <c r="E40" s="90" t="s">
+      <c r="D40" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="E40" s="87" t="s">
         <v>98</v>
       </c>
-      <c r="F40" s="130" t="s">
-        <v>200</v>
-      </c>
-      <c r="G40" s="112" t="s">
+      <c r="F40" s="123" t="s">
+        <v>199</v>
+      </c>
+      <c r="G40" s="104" t="s">
+        <v>171</v>
+      </c>
+      <c r="H40" s="52" t="s">
+        <v>183</v>
+      </c>
+      <c r="I40" s="11" t="s">
         <v>172</v>
       </c>
-      <c r="H40" s="17" t="s">
+      <c r="J40" s="52" t="s">
         <v>184</v>
       </c>
-      <c r="I40" s="16" t="s">
-        <v>173</v>
-      </c>
-      <c r="J40" s="17" t="s">
-        <v>185</v>
-      </c>
-      <c r="K40" s="16" t="s">
-        <v>175</v>
-      </c>
-      <c r="L40" s="17" t="s">
-        <v>187</v>
+      <c r="K40" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="L40" s="52" t="s">
+        <v>186</v>
       </c>
       <c r="M40" s="1"/>
       <c r="N40" s="1"/>
@@ -5249,41 +5264,39 @@
       <c r="AA40" s="1"/>
     </row>
     <row r="41" spans="1:27" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="36" t="s">
-        <v>101</v>
-      </c>
-      <c r="B41" s="37" t="s">
-        <v>102</v>
-      </c>
-      <c r="C41" s="37" t="s">
+      <c r="A41" s="24"/>
+      <c r="B41" s="25" t="s">
+        <v>96</v>
+      </c>
+      <c r="C41" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D41" s="39" t="s">
-        <v>103</v>
-      </c>
-      <c r="E41" s="92" t="s">
-        <v>104</v>
-      </c>
-      <c r="F41" s="124" t="s">
-        <v>105</v>
-      </c>
-      <c r="G41" s="105" t="s">
+      <c r="D41" s="74" t="s">
+        <v>100</v>
+      </c>
+      <c r="E41" s="88" t="s">
+        <v>98</v>
+      </c>
+      <c r="F41" s="128" t="s">
+        <v>199</v>
+      </c>
+      <c r="G41" s="110" t="s">
+        <v>171</v>
+      </c>
+      <c r="H41" s="17" t="s">
         <v>183</v>
       </c>
-      <c r="H41" s="71" t="s">
-        <v>298</v>
-      </c>
-      <c r="I41" s="70" t="s">
-        <v>173</v>
-      </c>
-      <c r="J41" s="71" t="s">
-        <v>185</v>
-      </c>
-      <c r="K41" s="70" t="s">
-        <v>201</v>
-      </c>
-      <c r="L41" s="71" t="s">
-        <v>202</v>
+      <c r="I41" s="16" t="s">
+        <v>172</v>
+      </c>
+      <c r="J41" s="17" t="s">
+        <v>184</v>
+      </c>
+      <c r="K41" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="L41" s="17" t="s">
+        <v>186</v>
       </c>
       <c r="M41" s="1"/>
       <c r="N41" s="1"/>
@@ -5302,39 +5315,41 @@
       <c r="AA41" s="1"/>
     </row>
     <row r="42" spans="1:27" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="25"/>
-      <c r="B42" s="19" t="s">
+      <c r="A42" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="B42" s="35" t="s">
         <v>102</v>
       </c>
-      <c r="C42" s="19" t="s">
+      <c r="C42" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="D42" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="E42" s="89" t="s">
+      <c r="D42" s="37" t="s">
+        <v>103</v>
+      </c>
+      <c r="E42" s="90" t="s">
         <v>104</v>
       </c>
-      <c r="F42" s="125" t="s">
+      <c r="F42" s="122" t="s">
         <v>105</v>
       </c>
-      <c r="G42" s="105" t="s">
-        <v>183</v>
-      </c>
-      <c r="H42" s="73" t="s">
-        <v>298</v>
-      </c>
-      <c r="I42" s="70" t="s">
-        <v>173</v>
-      </c>
-      <c r="J42" s="54" t="s">
-        <v>185</v>
-      </c>
-      <c r="K42" s="70" t="s">
+      <c r="G42" s="103" t="s">
+        <v>182</v>
+      </c>
+      <c r="H42" s="69" t="s">
+        <v>296</v>
+      </c>
+      <c r="I42" s="68" t="s">
+        <v>172</v>
+      </c>
+      <c r="J42" s="69" t="s">
+        <v>184</v>
+      </c>
+      <c r="K42" s="68" t="s">
+        <v>200</v>
+      </c>
+      <c r="L42" s="69" t="s">
         <v>201</v>
-      </c>
-      <c r="L42" s="71" t="s">
-        <v>202</v>
       </c>
       <c r="M42" s="1"/>
       <c r="N42" s="1"/>
@@ -5353,7 +5368,7 @@
       <c r="AA42" s="1"/>
     </row>
     <row r="43" spans="1:27" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="25"/>
+      <c r="A43" s="23"/>
       <c r="B43" s="19" t="s">
         <v>102</v>
       </c>
@@ -5361,31 +5376,31 @@
         <v>8</v>
       </c>
       <c r="D43" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="E43" s="89" t="s">
+        <v>106</v>
+      </c>
+      <c r="E43" s="87" t="s">
         <v>104</v>
       </c>
-      <c r="F43" s="125" t="s">
+      <c r="F43" s="123" t="s">
         <v>105</v>
       </c>
-      <c r="G43" s="105" t="s">
-        <v>183</v>
-      </c>
-      <c r="H43" s="73" t="s">
-        <v>298</v>
-      </c>
-      <c r="I43" s="70" t="s">
-        <v>173</v>
-      </c>
-      <c r="J43" s="54" t="s">
-        <v>185</v>
-      </c>
-      <c r="K43" s="70" t="s">
+      <c r="G43" s="103" t="s">
+        <v>182</v>
+      </c>
+      <c r="H43" s="71" t="s">
+        <v>296</v>
+      </c>
+      <c r="I43" s="68" t="s">
+        <v>172</v>
+      </c>
+      <c r="J43" s="52" t="s">
+        <v>184</v>
+      </c>
+      <c r="K43" s="68" t="s">
+        <v>200</v>
+      </c>
+      <c r="L43" s="69" t="s">
         <v>201</v>
-      </c>
-      <c r="L43" s="71" t="s">
-        <v>202</v>
       </c>
       <c r="M43" s="1"/>
       <c r="N43" s="1"/>
@@ -5404,7 +5419,7 @@
       <c r="AA43" s="1"/>
     </row>
     <row r="44" spans="1:27" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="25"/>
+      <c r="A44" s="23"/>
       <c r="B44" s="19" t="s">
         <v>102</v>
       </c>
@@ -5412,31 +5427,31 @@
         <v>8</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="E44" s="89" t="s">
+        <v>107</v>
+      </c>
+      <c r="E44" s="87" t="s">
         <v>104</v>
       </c>
-      <c r="F44" s="125" t="s">
+      <c r="F44" s="123" t="s">
         <v>105</v>
       </c>
-      <c r="G44" s="105" t="s">
-        <v>183</v>
-      </c>
-      <c r="H44" s="73" t="s">
-        <v>298</v>
-      </c>
-      <c r="I44" s="70" t="s">
-        <v>173</v>
-      </c>
-      <c r="J44" s="54" t="s">
-        <v>185</v>
-      </c>
-      <c r="K44" s="70" t="s">
+      <c r="G44" s="103" t="s">
+        <v>182</v>
+      </c>
+      <c r="H44" s="71" t="s">
+        <v>296</v>
+      </c>
+      <c r="I44" s="68" t="s">
+        <v>172</v>
+      </c>
+      <c r="J44" s="52" t="s">
+        <v>184</v>
+      </c>
+      <c r="K44" s="68" t="s">
+        <v>200</v>
+      </c>
+      <c r="L44" s="69" t="s">
         <v>201</v>
-      </c>
-      <c r="L44" s="71" t="s">
-        <v>202</v>
       </c>
       <c r="M44" s="1"/>
       <c r="N44" s="1"/>
@@ -5455,7 +5470,7 @@
       <c r="AA44" s="1"/>
     </row>
     <row r="45" spans="1:27" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="25"/>
+      <c r="A45" s="23"/>
       <c r="B45" s="19" t="s">
         <v>102</v>
       </c>
@@ -5463,31 +5478,31 @@
         <v>8</v>
       </c>
       <c r="D45" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="E45" s="89" t="s">
+        <v>108</v>
+      </c>
+      <c r="E45" s="87" t="s">
         <v>104</v>
       </c>
-      <c r="F45" s="125" t="s">
+      <c r="F45" s="123" t="s">
         <v>105</v>
       </c>
-      <c r="G45" s="105" t="s">
-        <v>183</v>
-      </c>
-      <c r="H45" s="73" t="s">
-        <v>298</v>
-      </c>
-      <c r="I45" s="70" t="s">
-        <v>173</v>
-      </c>
-      <c r="J45" s="54" t="s">
-        <v>185</v>
-      </c>
-      <c r="K45" s="70" t="s">
+      <c r="G45" s="103" t="s">
+        <v>182</v>
+      </c>
+      <c r="H45" s="71" t="s">
+        <v>296</v>
+      </c>
+      <c r="I45" s="68" t="s">
+        <v>172</v>
+      </c>
+      <c r="J45" s="52" t="s">
+        <v>184</v>
+      </c>
+      <c r="K45" s="68" t="s">
+        <v>200</v>
+      </c>
+      <c r="L45" s="69" t="s">
         <v>201</v>
-      </c>
-      <c r="L45" s="71" t="s">
-        <v>202</v>
       </c>
       <c r="M45" s="1"/>
       <c r="N45" s="1"/>
@@ -5506,7 +5521,7 @@
       <c r="AA45" s="1"/>
     </row>
     <row r="46" spans="1:27" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="25"/>
+      <c r="A46" s="23"/>
       <c r="B46" s="19" t="s">
         <v>102</v>
       </c>
@@ -5514,31 +5529,31 @@
         <v>8</v>
       </c>
       <c r="D46" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="E46" s="89" t="s">
+        <v>109</v>
+      </c>
+      <c r="E46" s="87" t="s">
         <v>104</v>
       </c>
-      <c r="F46" s="125" t="s">
+      <c r="F46" s="123" t="s">
         <v>105</v>
       </c>
-      <c r="G46" s="105" t="s">
-        <v>183</v>
-      </c>
-      <c r="H46" s="73" t="s">
-        <v>298</v>
-      </c>
-      <c r="I46" s="70" t="s">
-        <v>173</v>
-      </c>
-      <c r="J46" s="54" t="s">
-        <v>185</v>
-      </c>
-      <c r="K46" s="70" t="s">
+      <c r="G46" s="103" t="s">
+        <v>182</v>
+      </c>
+      <c r="H46" s="71" t="s">
+        <v>296</v>
+      </c>
+      <c r="I46" s="68" t="s">
+        <v>172</v>
+      </c>
+      <c r="J46" s="52" t="s">
+        <v>184</v>
+      </c>
+      <c r="K46" s="68" t="s">
+        <v>200</v>
+      </c>
+      <c r="L46" s="69" t="s">
         <v>201</v>
-      </c>
-      <c r="L46" s="71" t="s">
-        <v>202</v>
       </c>
       <c r="M46" s="1"/>
       <c r="N46" s="1"/>
@@ -5557,39 +5572,39 @@
       <c r="AA46" s="1"/>
     </row>
     <row r="47" spans="1:27" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="26"/>
-      <c r="B47" s="27" t="s">
+      <c r="A47" s="23"/>
+      <c r="B47" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="C47" s="27" t="s">
+      <c r="C47" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="D47" s="15" t="s">
-        <v>160</v>
-      </c>
-      <c r="E47" s="90" t="s">
+      <c r="D47" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="E47" s="87" t="s">
         <v>104</v>
       </c>
-      <c r="F47" s="130" t="s">
+      <c r="F47" s="123" t="s">
         <v>105</v>
       </c>
-      <c r="G47" s="105" t="s">
-        <v>183</v>
-      </c>
-      <c r="H47" s="17" t="s">
-        <v>298</v>
-      </c>
-      <c r="I47" s="70" t="s">
-        <v>173</v>
-      </c>
-      <c r="J47" s="17" t="s">
-        <v>185</v>
-      </c>
-      <c r="K47" s="70" t="s">
+      <c r="G47" s="103" t="s">
+        <v>182</v>
+      </c>
+      <c r="H47" s="71" t="s">
+        <v>296</v>
+      </c>
+      <c r="I47" s="68" t="s">
+        <v>172</v>
+      </c>
+      <c r="J47" s="52" t="s">
+        <v>184</v>
+      </c>
+      <c r="K47" s="68" t="s">
+        <v>200</v>
+      </c>
+      <c r="L47" s="69" t="s">
         <v>201</v>
-      </c>
-      <c r="L47" s="71" t="s">
-        <v>202</v>
       </c>
       <c r="M47" s="1"/>
       <c r="N47" s="1"/>
@@ -5608,24 +5623,40 @@
       <c r="AA47" s="1"/>
     </row>
     <row r="48" spans="1:27" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="48" t="s">
-        <v>114</v>
-      </c>
-      <c r="B48" s="49" t="s">
-        <v>115</v>
-      </c>
-      <c r="C48" s="49" t="s">
+      <c r="A48" s="24"/>
+      <c r="B48" s="25" t="s">
+        <v>102</v>
+      </c>
+      <c r="C48" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D48" s="52"/>
-      <c r="E48" s="102"/>
-      <c r="F48" s="133"/>
-      <c r="G48" s="115"/>
-      <c r="H48" s="53"/>
-      <c r="I48" s="52"/>
-      <c r="J48" s="53"/>
-      <c r="K48" s="52"/>
-      <c r="L48" s="53"/>
+      <c r="D48" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="E48" s="88" t="s">
+        <v>104</v>
+      </c>
+      <c r="F48" s="128" t="s">
+        <v>105</v>
+      </c>
+      <c r="G48" s="103" t="s">
+        <v>182</v>
+      </c>
+      <c r="H48" s="17" t="s">
+        <v>296</v>
+      </c>
+      <c r="I48" s="68" t="s">
+        <v>172</v>
+      </c>
+      <c r="J48" s="17" t="s">
+        <v>184</v>
+      </c>
+      <c r="K48" s="68" t="s">
+        <v>200</v>
+      </c>
+      <c r="L48" s="69" t="s">
+        <v>201</v>
+      </c>
       <c r="M48" s="1"/>
       <c r="N48" s="1"/>
       <c r="O48" s="1"/>
@@ -5643,42 +5674,24 @@
       <c r="AA48" s="1"/>
     </row>
     <row r="49" spans="1:27" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="41" t="s">
-        <v>116</v>
-      </c>
-      <c r="B49" s="42" t="s">
-        <v>117</v>
-      </c>
-      <c r="C49" s="42" t="s">
+      <c r="A49" s="46" t="s">
+        <v>114</v>
+      </c>
+      <c r="B49" s="47" t="s">
+        <v>115</v>
+      </c>
+      <c r="C49" s="47" t="s">
         <v>8</v>
       </c>
-      <c r="D49" s="43" t="s">
-        <v>118</v>
-      </c>
-      <c r="E49" s="91" t="s">
-        <v>119</v>
-      </c>
-      <c r="F49" s="134" t="s">
-        <v>120</v>
-      </c>
-      <c r="G49" s="116" t="s">
-        <v>178</v>
-      </c>
-      <c r="H49" s="79" t="s">
-        <v>190</v>
-      </c>
-      <c r="I49" s="47" t="s">
-        <v>173</v>
-      </c>
-      <c r="J49" s="79" t="s">
-        <v>185</v>
-      </c>
-      <c r="K49" s="47" t="s">
-        <v>179</v>
-      </c>
-      <c r="L49" s="79" t="s">
-        <v>191</v>
-      </c>
+      <c r="D49" s="50"/>
+      <c r="E49" s="100"/>
+      <c r="F49" s="131"/>
+      <c r="G49" s="113"/>
+      <c r="H49" s="51"/>
+      <c r="I49" s="50"/>
+      <c r="J49" s="51"/>
+      <c r="K49" s="50"/>
+      <c r="L49" s="51"/>
       <c r="M49" s="1"/>
       <c r="N49" s="1"/>
       <c r="O49" s="1"/>
@@ -5696,26 +5709,42 @@
       <c r="AA49" s="1"/>
     </row>
     <row r="50" spans="1:27" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="36" t="s">
-        <v>149</v>
-      </c>
-      <c r="B50" s="175" t="s">
-        <v>150</v>
-      </c>
-      <c r="C50" s="175" t="s">
+      <c r="A50" s="39" t="s">
+        <v>116</v>
+      </c>
+      <c r="B50" s="40" t="s">
+        <v>117</v>
+      </c>
+      <c r="C50" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="D50" s="46" t="s">
-        <v>151</v>
-      </c>
-      <c r="E50" s="92"/>
-      <c r="F50" s="135"/>
-      <c r="G50" s="117"/>
-      <c r="H50" s="40"/>
-      <c r="I50" s="39"/>
-      <c r="J50" s="40"/>
-      <c r="K50" s="39"/>
-      <c r="L50" s="40"/>
+      <c r="D50" s="41" t="s">
+        <v>118</v>
+      </c>
+      <c r="E50" s="89" t="s">
+        <v>119</v>
+      </c>
+      <c r="F50" s="132" t="s">
+        <v>120</v>
+      </c>
+      <c r="G50" s="114" t="s">
+        <v>177</v>
+      </c>
+      <c r="H50" s="77" t="s">
+        <v>189</v>
+      </c>
+      <c r="I50" s="45" t="s">
+        <v>172</v>
+      </c>
+      <c r="J50" s="77" t="s">
+        <v>184</v>
+      </c>
+      <c r="K50" s="45" t="s">
+        <v>178</v>
+      </c>
+      <c r="L50" s="77" t="s">
+        <v>190</v>
+      </c>
       <c r="M50" s="1"/>
       <c r="N50" s="1"/>
       <c r="O50" s="1"/>
@@ -5733,20 +5762,26 @@
       <c r="AA50" s="1"/>
     </row>
     <row r="51" spans="1:27" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="77"/>
-      <c r="B51" s="176"/>
-      <c r="C51" s="177"/>
-      <c r="D51" s="33" t="s">
-        <v>152</v>
-      </c>
-      <c r="E51" s="93"/>
-      <c r="F51" s="136"/>
-      <c r="G51" s="118"/>
-      <c r="H51" s="35"/>
-      <c r="I51" s="34"/>
-      <c r="J51" s="35"/>
-      <c r="K51" s="34"/>
-      <c r="L51" s="35"/>
+      <c r="A51" s="34" t="s">
+        <v>148</v>
+      </c>
+      <c r="B51" s="173" t="s">
+        <v>149</v>
+      </c>
+      <c r="C51" s="173" t="s">
+        <v>8</v>
+      </c>
+      <c r="D51" s="44" t="s">
+        <v>150</v>
+      </c>
+      <c r="E51" s="90"/>
+      <c r="F51" s="133"/>
+      <c r="G51" s="115"/>
+      <c r="H51" s="38"/>
+      <c r="I51" s="37"/>
+      <c r="J51" s="38"/>
+      <c r="K51" s="37"/>
+      <c r="L51" s="38"/>
       <c r="M51" s="1"/>
       <c r="N51" s="1"/>
       <c r="O51" s="1"/>
@@ -5764,42 +5799,20 @@
       <c r="AA51" s="1"/>
     </row>
     <row r="52" spans="1:27" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="41" t="s">
-        <v>121</v>
-      </c>
-      <c r="B52" s="42" t="s">
-        <v>122</v>
-      </c>
-      <c r="C52" s="42" t="s">
-        <v>8</v>
-      </c>
-      <c r="D52" s="43" t="s">
-        <v>123</v>
-      </c>
-      <c r="E52" s="91" t="s">
-        <v>124</v>
-      </c>
-      <c r="F52" s="123" t="s">
-        <v>9</v>
-      </c>
-      <c r="G52" s="104" t="s">
-        <v>172</v>
-      </c>
-      <c r="H52" s="45" t="s">
-        <v>184</v>
-      </c>
-      <c r="I52" s="44" t="s">
-        <v>173</v>
-      </c>
-      <c r="J52" s="45" t="s">
-        <v>185</v>
-      </c>
-      <c r="K52" s="44" t="s">
-        <v>175</v>
-      </c>
-      <c r="L52" s="45" t="s">
-        <v>187</v>
-      </c>
+      <c r="A52" s="75"/>
+      <c r="B52" s="174"/>
+      <c r="C52" s="175"/>
+      <c r="D52" s="31" t="s">
+        <v>151</v>
+      </c>
+      <c r="E52" s="91"/>
+      <c r="F52" s="134"/>
+      <c r="G52" s="116"/>
+      <c r="H52" s="33"/>
+      <c r="I52" s="32"/>
+      <c r="J52" s="33"/>
+      <c r="K52" s="32"/>
+      <c r="L52" s="33"/>
       <c r="M52" s="1"/>
       <c r="N52" s="1"/>
       <c r="O52" s="1"/>
@@ -5817,26 +5830,42 @@
       <c r="AA52" s="1"/>
     </row>
     <row r="53" spans="1:27" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="36" t="s">
-        <v>125</v>
-      </c>
-      <c r="B53" s="37" t="s">
-        <v>126</v>
-      </c>
-      <c r="C53" s="37" t="s">
+      <c r="A53" s="39" t="s">
+        <v>121</v>
+      </c>
+      <c r="B53" s="40" t="s">
+        <v>122</v>
+      </c>
+      <c r="C53" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="D53" s="38" t="s">
-        <v>153</v>
-      </c>
-      <c r="E53" s="92"/>
-      <c r="F53" s="135"/>
-      <c r="G53" s="117"/>
-      <c r="H53" s="40"/>
-      <c r="I53" s="39"/>
-      <c r="J53" s="40"/>
-      <c r="K53" s="39"/>
-      <c r="L53" s="40"/>
+      <c r="D53" s="41" t="s">
+        <v>123</v>
+      </c>
+      <c r="E53" s="89" t="s">
+        <v>124</v>
+      </c>
+      <c r="F53" s="121" t="s">
+        <v>9</v>
+      </c>
+      <c r="G53" s="102" t="s">
+        <v>171</v>
+      </c>
+      <c r="H53" s="43" t="s">
+        <v>183</v>
+      </c>
+      <c r="I53" s="42" t="s">
+        <v>172</v>
+      </c>
+      <c r="J53" s="43" t="s">
+        <v>184</v>
+      </c>
+      <c r="K53" s="42" t="s">
+        <v>174</v>
+      </c>
+      <c r="L53" s="43" t="s">
+        <v>186</v>
+      </c>
       <c r="M53" s="1"/>
       <c r="N53" s="1"/>
       <c r="O53" s="1"/>
@@ -5854,24 +5883,26 @@
       <c r="AA53" s="1"/>
     </row>
     <row r="54" spans="1:27" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="25"/>
-      <c r="B54" s="19" t="s">
+      <c r="A54" s="34" t="s">
+        <v>125</v>
+      </c>
+      <c r="B54" s="35" t="s">
         <v>126</v>
       </c>
-      <c r="C54" s="19" t="s">
+      <c r="C54" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="D54" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="E54" s="89"/>
-      <c r="F54" s="137"/>
-      <c r="G54" s="119"/>
-      <c r="H54" s="28"/>
-      <c r="I54" s="10"/>
-      <c r="J54" s="28"/>
-      <c r="K54" s="10"/>
-      <c r="L54" s="28"/>
+      <c r="D54" s="36" t="s">
+        <v>152</v>
+      </c>
+      <c r="E54" s="90"/>
+      <c r="F54" s="133"/>
+      <c r="G54" s="115"/>
+      <c r="H54" s="38"/>
+      <c r="I54" s="37"/>
+      <c r="J54" s="38"/>
+      <c r="K54" s="37"/>
+      <c r="L54" s="38"/>
       <c r="M54" s="1"/>
       <c r="N54" s="1"/>
       <c r="O54" s="1"/>
@@ -5889,24 +5920,24 @@
       <c r="AA54" s="1"/>
     </row>
     <row r="55" spans="1:27" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="25"/>
+      <c r="A55" s="23"/>
       <c r="B55" s="19" t="s">
         <v>126</v>
       </c>
       <c r="C55" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="D55" s="29" t="s">
-        <v>154</v>
-      </c>
-      <c r="E55" s="89"/>
-      <c r="F55" s="137"/>
-      <c r="G55" s="119"/>
-      <c r="H55" s="28"/>
+      <c r="D55" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="E55" s="87"/>
+      <c r="F55" s="135"/>
+      <c r="G55" s="117"/>
+      <c r="H55" s="26"/>
       <c r="I55" s="10"/>
-      <c r="J55" s="28"/>
+      <c r="J55" s="26"/>
       <c r="K55" s="10"/>
-      <c r="L55" s="28"/>
+      <c r="L55" s="26"/>
       <c r="M55" s="1"/>
       <c r="N55" s="1"/>
       <c r="O55" s="1"/>
@@ -5924,24 +5955,24 @@
       <c r="AA55" s="1"/>
     </row>
     <row r="56" spans="1:27" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="25"/>
+      <c r="A56" s="23"/>
       <c r="B56" s="19" t="s">
         <v>126</v>
       </c>
       <c r="C56" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="D56" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="E56" s="89"/>
-      <c r="F56" s="137"/>
-      <c r="G56" s="119"/>
-      <c r="H56" s="28"/>
+      <c r="D56" s="27" t="s">
+        <v>153</v>
+      </c>
+      <c r="E56" s="87"/>
+      <c r="F56" s="135"/>
+      <c r="G56" s="117"/>
+      <c r="H56" s="26"/>
       <c r="I56" s="10"/>
-      <c r="J56" s="28"/>
+      <c r="J56" s="26"/>
       <c r="K56" s="10"/>
-      <c r="L56" s="28"/>
+      <c r="L56" s="26"/>
       <c r="M56" s="1"/>
       <c r="N56" s="1"/>
       <c r="O56" s="1"/>
@@ -5959,24 +5990,24 @@
       <c r="AA56" s="1"/>
     </row>
     <row r="57" spans="1:27" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="25"/>
+      <c r="A57" s="23"/>
       <c r="B57" s="19" t="s">
         <v>126</v>
       </c>
       <c r="C57" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="D57" s="29" t="s">
-        <v>157</v>
-      </c>
-      <c r="E57" s="89"/>
-      <c r="F57" s="137"/>
-      <c r="G57" s="119"/>
-      <c r="H57" s="28"/>
+      <c r="D57" s="28" t="s">
+        <v>155</v>
+      </c>
+      <c r="E57" s="87"/>
+      <c r="F57" s="135"/>
+      <c r="G57" s="117"/>
+      <c r="H57" s="26"/>
       <c r="I57" s="10"/>
-      <c r="J57" s="28"/>
+      <c r="J57" s="26"/>
       <c r="K57" s="10"/>
-      <c r="L57" s="28"/>
+      <c r="L57" s="26"/>
       <c r="M57" s="1"/>
       <c r="N57" s="1"/>
       <c r="O57" s="1"/>
@@ -5994,24 +6025,24 @@
       <c r="AA57" s="1"/>
     </row>
     <row r="58" spans="1:27" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="26"/>
-      <c r="B58" s="27" t="s">
+      <c r="A58" s="23"/>
+      <c r="B58" s="19" t="s">
         <v>126</v>
       </c>
-      <c r="C58" s="27" t="s">
+      <c r="C58" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="D58" s="31" t="s">
-        <v>155</v>
-      </c>
-      <c r="E58" s="90"/>
-      <c r="F58" s="138"/>
-      <c r="G58" s="120"/>
-      <c r="H58" s="32"/>
-      <c r="I58" s="15"/>
-      <c r="J58" s="32"/>
-      <c r="K58" s="15"/>
-      <c r="L58" s="32"/>
+      <c r="D58" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="E58" s="87"/>
+      <c r="F58" s="135"/>
+      <c r="G58" s="117"/>
+      <c r="H58" s="26"/>
+      <c r="I58" s="10"/>
+      <c r="J58" s="26"/>
+      <c r="K58" s="10"/>
+      <c r="L58" s="26"/>
       <c r="M58" s="1"/>
       <c r="N58" s="1"/>
       <c r="O58" s="1"/>
@@ -6028,19 +6059,25 @@
       <c r="Z58" s="1"/>
       <c r="AA58" s="1"/>
     </row>
-    <row r="59" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="18"/>
-      <c r="B59" s="18"/>
-      <c r="C59" s="18"/>
-      <c r="D59" s="18"/>
-      <c r="E59" s="18"/>
-      <c r="F59" s="18"/>
-      <c r="G59" s="18"/>
-      <c r="H59" s="18"/>
-      <c r="I59" s="18"/>
-      <c r="J59" s="18"/>
-      <c r="K59" s="18"/>
-      <c r="L59" s="18"/>
+    <row r="59" spans="1:27" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="24"/>
+      <c r="B59" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="C59" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D59" s="29" t="s">
+        <v>154</v>
+      </c>
+      <c r="E59" s="88"/>
+      <c r="F59" s="136"/>
+      <c r="G59" s="118"/>
+      <c r="H59" s="30"/>
+      <c r="I59" s="15"/>
+      <c r="J59" s="30"/>
+      <c r="K59" s="15"/>
+      <c r="L59" s="30"/>
       <c r="M59" s="1"/>
       <c r="N59" s="1"/>
       <c r="O59" s="1"/>
@@ -6058,18 +6095,18 @@
       <c r="AA59" s="1"/>
     </row>
     <row r="60" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="1"/>
-      <c r="B60" s="1"/>
-      <c r="C60" s="1"/>
-      <c r="D60" s="1"/>
-      <c r="E60" s="1"/>
-      <c r="F60" s="1"/>
-      <c r="G60" s="1"/>
-      <c r="H60" s="1"/>
-      <c r="I60" s="1"/>
-      <c r="J60" s="1"/>
-      <c r="K60" s="1"/>
-      <c r="L60" s="1"/>
+      <c r="A60" s="18"/>
+      <c r="B60" s="18"/>
+      <c r="C60" s="18"/>
+      <c r="D60" s="18"/>
+      <c r="E60" s="18"/>
+      <c r="F60" s="18"/>
+      <c r="G60" s="18"/>
+      <c r="H60" s="18"/>
+      <c r="I60" s="18"/>
+      <c r="J60" s="18"/>
+      <c r="K60" s="18"/>
+      <c r="L60" s="18"/>
       <c r="M60" s="1"/>
       <c r="N60" s="1"/>
       <c r="O60" s="1"/>
@@ -32360,10 +32397,39 @@
       <c r="Z966" s="1"/>
       <c r="AA966" s="1"/>
     </row>
+    <row r="967" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A967" s="1"/>
+      <c r="B967" s="1"/>
+      <c r="C967" s="1"/>
+      <c r="D967" s="1"/>
+      <c r="E967" s="1"/>
+      <c r="F967" s="1"/>
+      <c r="G967" s="1"/>
+      <c r="H967" s="1"/>
+      <c r="I967" s="1"/>
+      <c r="J967" s="1"/>
+      <c r="K967" s="1"/>
+      <c r="L967" s="1"/>
+      <c r="M967" s="1"/>
+      <c r="N967" s="1"/>
+      <c r="O967" s="1"/>
+      <c r="P967" s="1"/>
+      <c r="Q967" s="1"/>
+      <c r="R967" s="1"/>
+      <c r="S967" s="1"/>
+      <c r="T967" s="1"/>
+      <c r="U967" s="1"/>
+      <c r="V967" s="1"/>
+      <c r="W967" s="1"/>
+      <c r="X967" s="1"/>
+      <c r="Y967" s="1"/>
+      <c r="Z967" s="1"/>
+      <c r="AA967" s="1"/>
+    </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="B50:B51"/>
-    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="B51:B52"/>
+    <mergeCell ref="C51:C52"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="I1:J1"/>
     <mergeCell ref="K1:L1"/>
@@ -32447,12 +32513,12 @@
       <c r="Y2" s="1"/>
       <c r="Z2" s="1"/>
     </row>
-    <row r="3" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:26" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="8" t="s">
         <v>14</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>131</v>
+        <v>303</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -32481,10 +32547,10 @@
     </row>
     <row r="4" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="8" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
@@ -32516,7 +32582,7 @@
         <v>30</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
@@ -32545,10 +32611,10 @@
     </row>
     <row r="6" spans="1:26" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
@@ -32580,7 +32646,7 @@
         <v>62</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
@@ -32612,7 +32678,7 @@
         <v>77</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
@@ -32644,7 +32710,7 @@
         <v>30</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
@@ -32676,7 +32742,7 @@
         <v>48</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
@@ -32708,7 +32774,7 @@
         <v>51</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
@@ -32740,7 +32806,7 @@
         <v>54</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
@@ -32769,10 +32835,10 @@
     </row>
     <row r="13" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>165</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>166</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
@@ -32804,7 +32870,7 @@
         <v>57</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
@@ -32836,7 +32902,7 @@
         <v>67</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
@@ -32868,7 +32934,7 @@
         <v>72</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
@@ -32900,7 +32966,7 @@
         <v>83</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
@@ -32932,7 +32998,7 @@
         <v>92</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
@@ -32964,7 +33030,7 @@
         <v>105</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
@@ -32996,7 +33062,7 @@
         <v>111</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
@@ -33028,7 +33094,7 @@
         <v>112</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
@@ -33059,8 +33125,8 @@
       <c r="A22" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="B22" s="165" t="s">
-        <v>146</v>
+      <c r="B22" s="163" t="s">
+        <v>145</v>
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
@@ -33088,11 +33154,11 @@
       <c r="Z22" s="1"/>
     </row>
     <row r="23" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="164" t="s">
+      <c r="A23" s="162" t="s">
         <v>120</v>
       </c>
-      <c r="B23" s="166" t="s">
-        <v>147</v>
+      <c r="B23" s="164" t="s">
+        <v>146</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="1"/>
@@ -33120,10 +33186,10 @@
       <c r="Z23" s="1"/>
     </row>
     <row r="24" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="167" t="s">
-        <v>184</v>
-      </c>
-      <c r="B24" s="166"/>
+      <c r="A24" s="165" t="s">
+        <v>183</v>
+      </c>
+      <c r="B24" s="164"/>
       <c r="C24" s="9"/>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
@@ -33151,10 +33217,10 @@
     </row>
     <row r="25" spans="1:26" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="B25" s="168" t="s">
-        <v>293</v>
+        <v>184</v>
+      </c>
+      <c r="B25" s="166" t="s">
+        <v>291</v>
       </c>
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
@@ -33183,10 +33249,10 @@
     </row>
     <row r="26" spans="1:26" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="7" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
@@ -33215,10 +33281,10 @@
     </row>
     <row r="27" spans="1:26" ht="53.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="7" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
@@ -33247,10 +33313,10 @@
     </row>
     <row r="28" spans="1:26" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
@@ -33279,10 +33345,10 @@
     </row>
     <row r="29" spans="1:26" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="7" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
@@ -33311,10 +33377,10 @@
     </row>
     <row r="30" spans="1:26" ht="93" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
@@ -33343,10 +33409,10 @@
     </row>
     <row r="31" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="7" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
@@ -33375,10 +33441,10 @@
     </row>
     <row r="32" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="7" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
@@ -33407,10 +33473,10 @@
     </row>
     <row r="33" spans="1:26" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="7" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
@@ -33439,10 +33505,10 @@
     </row>
     <row r="34" spans="1:26" ht="66.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="7" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
@@ -33471,10 +33537,10 @@
     </row>
     <row r="35" spans="1:26" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="7" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
@@ -33503,10 +33569,10 @@
     </row>
     <row r="36" spans="1:26" ht="106.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="7" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
@@ -33535,10 +33601,10 @@
     </row>
     <row r="37" spans="1:26" ht="66.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="B37" s="2" t="s">
         <v>240</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>241</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
@@ -33567,7 +33633,7 @@
     </row>
     <row r="38" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" s="1"/>
@@ -33597,10 +33663,10 @@
     </row>
     <row r="39" spans="1:26" ht="79.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
@@ -33629,10 +33695,10 @@
     </row>
     <row r="40" spans="1:26" ht="79.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
@@ -33661,10 +33727,10 @@
     </row>
     <row r="41" spans="1:26" ht="106.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
@@ -33693,10 +33759,10 @@
     </row>
     <row r="42" spans="1:26" ht="106.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
@@ -33725,10 +33791,10 @@
     </row>
     <row r="43" spans="1:26" ht="79.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
@@ -33757,10 +33823,10 @@
     </row>
     <row r="44" spans="1:26" ht="79.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
@@ -33789,10 +33855,10 @@
     </row>
     <row r="45" spans="1:26" ht="145.80000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
@@ -33821,10 +33887,10 @@
     </row>
     <row r="46" spans="1:26" ht="66.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
@@ -33853,10 +33919,10 @@
     </row>
     <row r="47" spans="1:26" ht="79.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
@@ -33885,10 +33951,10 @@
     </row>
     <row r="48" spans="1:26" ht="119.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
@@ -33917,10 +33983,10 @@
     </row>
     <row r="49" spans="1:26" ht="79.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
@@ -33949,10 +34015,10 @@
     </row>
     <row r="50" spans="1:26" ht="198.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
@@ -33981,10 +34047,10 @@
     </row>
     <row r="51" spans="1:26" ht="119.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="B51" s="2" t="s">
         <v>242</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>243</v>
       </c>
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
@@ -61069,324 +61135,324 @@
   <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.33203125" style="153" customWidth="1"/>
-    <col min="2" max="2" width="105.6640625" style="156" customWidth="1"/>
-    <col min="3" max="3" width="111.6640625" style="156" customWidth="1"/>
-    <col min="4" max="16384" width="11.44140625" style="152"/>
+    <col min="1" max="1" width="19.33203125" style="151" customWidth="1"/>
+    <col min="2" max="2" width="105.6640625" style="154" customWidth="1"/>
+    <col min="3" max="3" width="111.6640625" style="154" customWidth="1"/>
+    <col min="4" max="16384" width="11.44140625" style="150"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="151" t="s">
+      <c r="A1" s="149" t="s">
         <v>128</v>
       </c>
-      <c r="B1" s="154" t="s">
+      <c r="B1" s="152" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="154" t="s">
+      <c r="C1" s="152" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="124.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="159" t="s">
+      <c r="A2" s="157" t="s">
+        <v>213</v>
+      </c>
+      <c r="B2" s="169" t="s">
+        <v>267</v>
+      </c>
+      <c r="C2" s="153"/>
+    </row>
+    <row r="3" spans="1:3" ht="152.4" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="156" t="s">
         <v>214</v>
       </c>
-      <c r="B2" s="171" t="s">
+      <c r="B3" s="169" t="s">
         <v>268</v>
       </c>
-      <c r="C2" s="155"/>
-    </row>
-    <row r="3" spans="1:3" ht="152.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="158" t="s">
+      <c r="C3" s="153"/>
+    </row>
+    <row r="4" spans="1:3" ht="138.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="156" t="s">
         <v>215</v>
       </c>
-      <c r="B3" s="171" t="s">
+      <c r="B4" s="169" t="s">
         <v>269</v>
       </c>
-      <c r="C3" s="155"/>
-    </row>
-    <row r="4" spans="1:3" ht="138.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="158" t="s">
+      <c r="C4" s="153"/>
+    </row>
+    <row r="5" spans="1:3" ht="249" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="156" t="s">
         <v>216</v>
       </c>
-      <c r="B4" s="171" t="s">
+      <c r="B5" s="169" t="s">
         <v>270</v>
       </c>
-      <c r="C4" s="155"/>
-    </row>
-    <row r="5" spans="1:3" ht="249" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="158" t="s">
+      <c r="C5" s="158" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="220.8" x14ac:dyDescent="0.25">
+      <c r="A6" s="155" t="s">
         <v>217</v>
       </c>
-      <c r="B5" s="171" t="s">
+      <c r="B6" s="170" t="s">
         <v>271</v>
       </c>
-      <c r="C5" s="160" t="s">
+      <c r="C6" s="158" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="220.8" x14ac:dyDescent="0.25">
-      <c r="A6" s="157" t="s">
+    <row r="7" spans="1:3" ht="179.4" x14ac:dyDescent="0.25">
+      <c r="A7" s="155" t="s">
         <v>218</v>
       </c>
-      <c r="B6" s="172" t="s">
+      <c r="B7" s="171" t="s">
         <v>272</v>
       </c>
-      <c r="C6" s="160" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="179.4" x14ac:dyDescent="0.25">
-      <c r="A7" s="157" t="s">
+      <c r="C7" s="153"/>
+    </row>
+    <row r="8" spans="1:3" ht="193.2" x14ac:dyDescent="0.25">
+      <c r="A8" s="155" t="s">
         <v>219</v>
       </c>
-      <c r="B7" s="173" t="s">
+      <c r="B8" s="171" t="s">
         <v>273</v>
       </c>
-      <c r="C7" s="155"/>
-    </row>
-    <row r="8" spans="1:3" ht="193.2" x14ac:dyDescent="0.25">
-      <c r="A8" s="157" t="s">
+      <c r="C8" s="153"/>
+    </row>
+    <row r="9" spans="1:3" ht="151.80000000000001" x14ac:dyDescent="0.25">
+      <c r="A9" s="155" t="s">
         <v>220</v>
       </c>
-      <c r="B8" s="173" t="s">
+      <c r="B9" s="171" t="s">
         <v>274</v>
       </c>
-      <c r="C8" s="155"/>
-    </row>
-    <row r="9" spans="1:3" ht="151.80000000000001" x14ac:dyDescent="0.25">
-      <c r="A9" s="157" t="s">
-        <v>221</v>
-      </c>
-      <c r="B9" s="173" t="s">
+      <c r="C9" s="153"/>
+    </row>
+    <row r="10" spans="1:3" ht="262.2" x14ac:dyDescent="0.25">
+      <c r="A10" s="155" t="s">
+        <v>224</v>
+      </c>
+      <c r="B10" s="159" t="s">
         <v>275</v>
       </c>
-      <c r="C9" s="155"/>
-    </row>
-    <row r="10" spans="1:3" ht="262.2" x14ac:dyDescent="0.25">
-      <c r="A10" s="157" t="s">
+      <c r="C10" s="153"/>
+    </row>
+    <row r="11" spans="1:3" ht="151.80000000000001" x14ac:dyDescent="0.25">
+      <c r="A11" s="155" t="s">
+        <v>258</v>
+      </c>
+      <c r="B11" s="171" t="s">
+        <v>276</v>
+      </c>
+      <c r="C11" s="153"/>
+    </row>
+    <row r="12" spans="1:3" ht="345" x14ac:dyDescent="0.25">
+      <c r="A12" s="155" t="s">
+        <v>259</v>
+      </c>
+      <c r="B12" s="159" t="s">
+        <v>277</v>
+      </c>
+      <c r="C12" s="158" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="151.80000000000001" x14ac:dyDescent="0.25">
+      <c r="A13" s="155" t="s">
         <v>225</v>
       </c>
-      <c r="B10" s="161" t="s">
-        <v>276</v>
-      </c>
-      <c r="C10" s="155"/>
-    </row>
-    <row r="11" spans="1:3" ht="151.80000000000001" x14ac:dyDescent="0.25">
-      <c r="A11" s="157" t="s">
-        <v>259</v>
-      </c>
-      <c r="B11" s="173" t="s">
-        <v>277</v>
-      </c>
-      <c r="C11" s="155"/>
-    </row>
-    <row r="12" spans="1:3" ht="345" x14ac:dyDescent="0.25">
-      <c r="A12" s="157" t="s">
-        <v>260</v>
-      </c>
-      <c r="B12" s="161" t="s">
+      <c r="B13" s="171" t="s">
         <v>278</v>
       </c>
-      <c r="C12" s="160" t="s">
+      <c r="C13" s="153"/>
+    </row>
+    <row r="14" spans="1:3" ht="138" x14ac:dyDescent="0.25">
+      <c r="A14" s="155" t="s">
+        <v>226</v>
+      </c>
+      <c r="B14" s="171" t="s">
+        <v>279</v>
+      </c>
+      <c r="C14" s="153"/>
+    </row>
+    <row r="15" spans="1:3" ht="220.8" x14ac:dyDescent="0.25">
+      <c r="A15" s="155" t="s">
+        <v>227</v>
+      </c>
+      <c r="B15" s="171" t="s">
+        <v>280</v>
+      </c>
+      <c r="C15" s="153"/>
+    </row>
+    <row r="16" spans="1:3" ht="96.6" x14ac:dyDescent="0.25">
+      <c r="A16" s="168" t="s">
+        <v>228</v>
+      </c>
+      <c r="B16" s="171" t="s">
+        <v>281</v>
+      </c>
+      <c r="C16" s="153"/>
+    </row>
+    <row r="17" spans="1:7" ht="165.6" x14ac:dyDescent="0.25">
+      <c r="A17" s="168" t="s">
+        <v>229</v>
+      </c>
+      <c r="B17" s="171" t="s">
+        <v>282</v>
+      </c>
+      <c r="C17" s="153"/>
+    </row>
+    <row r="18" spans="1:7" ht="249" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="167" t="s">
+        <v>230</v>
+      </c>
+      <c r="B18" s="172" t="s">
+        <v>270</v>
+      </c>
+      <c r="C18" s="158" t="s">
+        <v>233</v>
+      </c>
+      <c r="G18" s="160"/>
+    </row>
+    <row r="19" spans="1:7" ht="220.8" x14ac:dyDescent="0.25">
+      <c r="A19" s="155" t="s">
+        <v>231</v>
+      </c>
+      <c r="B19" s="170" t="s">
+        <v>283</v>
+      </c>
+      <c r="C19" s="158" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="110.4" x14ac:dyDescent="0.25">
+      <c r="A20" s="168" t="s">
+        <v>232</v>
+      </c>
+      <c r="B20" s="171" t="s">
+        <v>284</v>
+      </c>
+      <c r="C20" s="153"/>
+    </row>
+    <row r="21" spans="1:7" ht="220.8" x14ac:dyDescent="0.25">
+      <c r="A21" s="168" t="s">
+        <v>235</v>
+      </c>
+      <c r="B21" s="171" t="s">
+        <v>285</v>
+      </c>
+      <c r="C21" s="158" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="221.4" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="168" t="s">
+        <v>236</v>
+      </c>
+      <c r="B22" s="171" t="s">
+        <v>286</v>
+      </c>
+      <c r="C22" s="158" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="111" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="157" t="s">
+        <v>245</v>
+      </c>
+      <c r="B23" s="169" t="s">
+        <v>287</v>
+      </c>
+      <c r="C23" s="153"/>
+    </row>
+    <row r="24" spans="1:7" ht="165.6" x14ac:dyDescent="0.25">
+      <c r="A24" s="168" t="s">
+        <v>246</v>
+      </c>
+      <c r="B24" s="171" t="s">
+        <v>299</v>
+      </c>
+      <c r="C24" s="153"/>
+    </row>
+    <row r="25" spans="1:7" ht="110.4" x14ac:dyDescent="0.25">
+      <c r="A25" s="168" t="s">
+        <v>248</v>
+      </c>
+      <c r="B25" s="171" t="s">
+        <v>301</v>
+      </c>
+      <c r="C25" s="153"/>
+    </row>
+    <row r="26" spans="1:7" ht="96.6" x14ac:dyDescent="0.25">
+      <c r="A26" s="168" t="s">
+        <v>250</v>
+      </c>
+      <c r="B26" s="171" t="s">
+        <v>288</v>
+      </c>
+      <c r="C26" s="158" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="151.80000000000001" x14ac:dyDescent="0.25">
+      <c r="A27" s="151" t="s">
+        <v>251</v>
+      </c>
+      <c r="B27" s="158" t="s">
+        <v>289</v>
+      </c>
+      <c r="C27" s="158"/>
+    </row>
+    <row r="28" spans="1:7" ht="220.8" x14ac:dyDescent="0.25">
+      <c r="A28" s="151" t="s">
+        <v>253</v>
+      </c>
+      <c r="B28" s="158" t="s">
+        <v>290</v>
+      </c>
+      <c r="C28" s="158" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="96.6" x14ac:dyDescent="0.25">
+      <c r="A29" s="168" t="s">
+        <v>254</v>
+      </c>
+      <c r="B29" s="171" t="s">
+        <v>266</v>
+      </c>
+      <c r="C29" s="158" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="96.6" x14ac:dyDescent="0.25">
+      <c r="A30" s="168" t="s">
+        <v>256</v>
+      </c>
+      <c r="B30" s="171" t="s">
+        <v>265</v>
+      </c>
+      <c r="C30" s="158" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="193.2" x14ac:dyDescent="0.25">
+      <c r="A31" s="168" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" ht="151.80000000000001" x14ac:dyDescent="0.25">
-      <c r="A13" s="157" t="s">
-        <v>226</v>
-      </c>
-      <c r="B13" s="173" t="s">
-        <v>279</v>
-      </c>
-      <c r="C13" s="155"/>
-    </row>
-    <row r="14" spans="1:3" ht="138" x14ac:dyDescent="0.25">
-      <c r="A14" s="157" t="s">
-        <v>227</v>
-      </c>
-      <c r="B14" s="173" t="s">
-        <v>280</v>
-      </c>
-      <c r="C14" s="155"/>
-    </row>
-    <row r="15" spans="1:3" ht="220.8" x14ac:dyDescent="0.25">
-      <c r="A15" s="157" t="s">
-        <v>228</v>
-      </c>
-      <c r="B15" s="173" t="s">
-        <v>281</v>
-      </c>
-      <c r="C15" s="155"/>
-    </row>
-    <row r="16" spans="1:3" ht="96.6" x14ac:dyDescent="0.25">
-      <c r="A16" s="170" t="s">
-        <v>229</v>
-      </c>
-      <c r="B16" s="173" t="s">
-        <v>282</v>
-      </c>
-      <c r="C16" s="155"/>
-    </row>
-    <row r="17" spans="1:7" ht="165.6" x14ac:dyDescent="0.25">
-      <c r="A17" s="170" t="s">
-        <v>230</v>
-      </c>
-      <c r="B17" s="173" t="s">
-        <v>283</v>
-      </c>
-      <c r="C17" s="155"/>
-    </row>
-    <row r="18" spans="1:7" ht="249" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="169" t="s">
-        <v>231</v>
-      </c>
-      <c r="B18" s="174" t="s">
-        <v>271</v>
-      </c>
-      <c r="C18" s="160" t="s">
-        <v>234</v>
-      </c>
-      <c r="G18" s="162"/>
-    </row>
-    <row r="19" spans="1:7" ht="220.8" x14ac:dyDescent="0.25">
-      <c r="A19" s="157" t="s">
-        <v>232</v>
-      </c>
-      <c r="B19" s="172" t="s">
-        <v>284</v>
-      </c>
-      <c r="C19" s="160" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="110.4" x14ac:dyDescent="0.25">
-      <c r="A20" s="170" t="s">
-        <v>233</v>
-      </c>
-      <c r="B20" s="173" t="s">
-        <v>285</v>
-      </c>
-      <c r="C20" s="155"/>
-    </row>
-    <row r="21" spans="1:7" ht="220.8" x14ac:dyDescent="0.25">
-      <c r="A21" s="170" t="s">
-        <v>236</v>
-      </c>
-      <c r="B21" s="173" t="s">
-        <v>286</v>
-      </c>
-      <c r="C21" s="160" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="221.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="170" t="s">
-        <v>237</v>
-      </c>
-      <c r="B22" s="173" t="s">
-        <v>287</v>
-      </c>
-      <c r="C22" s="160" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="111" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="159" t="s">
-        <v>246</v>
-      </c>
-      <c r="B23" s="171" t="s">
-        <v>288</v>
-      </c>
-      <c r="C23" s="155"/>
-    </row>
-    <row r="24" spans="1:7" ht="165.6" x14ac:dyDescent="0.25">
-      <c r="A24" s="170" t="s">
-        <v>247</v>
-      </c>
-      <c r="B24" s="173" t="s">
-        <v>301</v>
-      </c>
-      <c r="C24" s="155"/>
-    </row>
-    <row r="25" spans="1:7" ht="110.4" x14ac:dyDescent="0.25">
-      <c r="A25" s="170" t="s">
-        <v>249</v>
-      </c>
-      <c r="B25" s="173" t="s">
-        <v>289</v>
-      </c>
-      <c r="C25" s="155"/>
-    </row>
-    <row r="26" spans="1:7" ht="96.6" x14ac:dyDescent="0.25">
-      <c r="A26" s="170" t="s">
-        <v>251</v>
-      </c>
-      <c r="B26" s="173" t="s">
-        <v>290</v>
-      </c>
-      <c r="C26" s="160" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="151.80000000000001" x14ac:dyDescent="0.25">
-      <c r="A27" s="153" t="s">
-        <v>252</v>
-      </c>
-      <c r="B27" s="160" t="s">
-        <v>291</v>
-      </c>
-      <c r="C27" s="160"/>
-    </row>
-    <row r="28" spans="1:7" ht="220.8" x14ac:dyDescent="0.25">
-      <c r="A28" s="153" t="s">
-        <v>254</v>
-      </c>
-      <c r="B28" s="160" t="s">
-        <v>292</v>
-      </c>
-      <c r="C28" s="160" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="96.6" x14ac:dyDescent="0.25">
-      <c r="A29" s="170" t="s">
-        <v>255</v>
-      </c>
-      <c r="B29" s="173" t="s">
-        <v>267</v>
-      </c>
-      <c r="C29" s="160" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="96.6" x14ac:dyDescent="0.25">
-      <c r="A30" s="170" t="s">
-        <v>257</v>
-      </c>
-      <c r="B30" s="173" t="s">
-        <v>266</v>
-      </c>
-      <c r="C30" s="160" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="193.2" x14ac:dyDescent="0.25">
-      <c r="A31" s="170" t="s">
+      <c r="B31" s="171" t="s">
+        <v>263</v>
+      </c>
+      <c r="C31" s="153"/>
+    </row>
+    <row r="32" spans="1:7" ht="193.2" x14ac:dyDescent="0.25">
+      <c r="A32" s="168" t="s">
         <v>262</v>
       </c>
-      <c r="B31" s="173" t="s">
+      <c r="B32" s="171" t="s">
         <v>264</v>
       </c>
-      <c r="C31" s="155"/>
-    </row>
-    <row r="32" spans="1:7" ht="193.2" x14ac:dyDescent="0.25">
-      <c r="A32" s="170" t="s">
-        <v>263</v>
-      </c>
-      <c r="B32" s="173" t="s">
-        <v>265</v>
-      </c>
-      <c r="C32" s="155"/>
+      <c r="C32" s="153"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/CotsList.xlsx
+++ b/data/CotsList.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rserghine\Projects React\DsiCenter_Excel\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC9A910E-9DEC-4A02-AFF6-68D0499B2123}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A484B30-2786-4BA1-802F-997E0F25B2F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{67F2D85F-F75B-4B61-9855-239B084B2F7E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{67F2D85F-F75B-4B61-9855-239B084B2F7E}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -2958,17 +2958,6 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -2984,6 +2973,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3354,18 +3354,18 @@
       <c r="F1" s="53" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="176" t="s">
+      <c r="G1" s="181" t="s">
         <v>167</v>
       </c>
-      <c r="H1" s="177"/>
-      <c r="I1" s="176" t="s">
+      <c r="H1" s="182"/>
+      <c r="I1" s="181" t="s">
         <v>168</v>
       </c>
-      <c r="J1" s="177"/>
-      <c r="K1" s="176" t="s">
+      <c r="J1" s="182"/>
+      <c r="K1" s="181" t="s">
         <v>169</v>
       </c>
-      <c r="L1" s="177"/>
+      <c r="L1" s="182"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
@@ -3427,14 +3427,14 @@
       <c r="A3" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="180" t="s">
+      <c r="B3" s="175" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="181" t="s">
+      <c r="C3" s="176" t="s">
         <v>8</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>302</v>
+        <v>12</v>
       </c>
       <c r="E3" s="12" t="s">
         <v>13</v>
@@ -3480,14 +3480,14 @@
       <c r="A4" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="180" t="s">
+      <c r="B4" s="175" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="182" t="s">
+      <c r="C4" s="177" t="s">
         <v>8</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>12</v>
+        <v>302</v>
       </c>
       <c r="E4" s="15" t="s">
         <v>13</v>
@@ -3545,25 +3545,25 @@
       <c r="E5" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="178" t="s">
+      <c r="F5" s="173" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="178" t="s">
+      <c r="G5" s="173" t="s">
         <v>171</v>
       </c>
-      <c r="H5" s="178" t="s">
+      <c r="H5" s="173" t="s">
         <v>183</v>
       </c>
-      <c r="I5" s="178" t="s">
+      <c r="I5" s="173" t="s">
         <v>172</v>
       </c>
-      <c r="J5" s="178" t="s">
+      <c r="J5" s="173" t="s">
         <v>184</v>
       </c>
-      <c r="K5" s="178" t="s">
+      <c r="K5" s="173" t="s">
         <v>174</v>
       </c>
-      <c r="L5" s="179" t="s">
+      <c r="L5" s="174" t="s">
         <v>186</v>
       </c>
       <c r="M5" s="9"/>
@@ -5765,10 +5765,10 @@
       <c r="A51" s="34" t="s">
         <v>148</v>
       </c>
-      <c r="B51" s="173" t="s">
+      <c r="B51" s="178" t="s">
         <v>149</v>
       </c>
-      <c r="C51" s="173" t="s">
+      <c r="C51" s="178" t="s">
         <v>8</v>
       </c>
       <c r="D51" s="44" t="s">
@@ -5800,8 +5800,8 @@
     </row>
     <row r="52" spans="1:27" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="75"/>
-      <c r="B52" s="174"/>
-      <c r="C52" s="175"/>
+      <c r="B52" s="179"/>
+      <c r="C52" s="180"/>
       <c r="D52" s="31" t="s">
         <v>151</v>
       </c>

--- a/data/CotsList.xlsx
+++ b/data/CotsList.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rserghine\Projects React\DsiCenter_Excel\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A484B30-2786-4BA1-802F-997E0F25B2F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FBC0F3F-1638-4A8E-8EA3-44188847631D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{67F2D85F-F75B-4B61-9855-239B084B2F7E}"/>
   </bookViews>
@@ -1496,11 +1496,11 @@
 </t>
   </si>
   <si>
-    <t>Altia Design (13,4_64b) EN</t>
+    <t>Check User is located in Europe, then Add user.
+If version 13 : send by mail : the manual "AltiaAccount-UserGuide.pdf" (in sns.corp\...\Application list\Altia Design 13.4)</t>
   </si>
   <si>
-    <t>Check User is located in Europe, then Add user.
-If version 13 : send by mail : the manual "AltiaAccount-UserGuide.pdf" (in sns.corp\...\Application list\Altia Design 13.4)</t>
+    <t>Altia Design (13.4_64b) EN</t>
   </si>
 </sst>
 </file>
@@ -3487,7 +3487,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E4" s="15" t="s">
         <v>13</v>
@@ -32518,7 +32518,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>

--- a/data/CotsList.xlsx
+++ b/data/CotsList.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rserghine\Projects React\DsiCenter_Excel\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FBC0F3F-1638-4A8E-8EA3-44188847631D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56C1F275-C4DD-40AA-809A-BCE952CF623C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{67F2D85F-F75B-4B61-9855-239B084B2F7E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{67F2D85F-F75B-4B61-9855-239B084B2F7E}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="700" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="704" uniqueCount="308">
   <si>
     <t>APPLICATION</t>
   </si>
@@ -1501,6 +1501,24 @@
   </si>
   <si>
     <t>Altia Design (13.4_64b) EN</t>
+  </si>
+  <si>
+    <t>AC 1B</t>
+  </si>
+  <si>
+    <t>WN 1B</t>
+  </si>
+  <si>
+    <t>Dear user,
+You have been added to the access group of "SOFTWARE".
+To install the application: Restart the PC, Wait 2 hours and Go to Pc Services or Software Center.
+We sent you, by mail, a manual to create a mandatory Altia account.
+Best regards</t>
+  </si>
+  <si>
+    <t>The user has been added to the access group of "SOFTWARE".
+To install the application: Restart the PC, Wait 2 hours and Go to Pc Services or  Software Center.
+We sent him, by mail, a manual to create an mandatory Altia account.</t>
   </si>
 </sst>
 </file>
@@ -3502,10 +3520,10 @@
         <v>183</v>
       </c>
       <c r="I4" s="16" t="s">
-        <v>172</v>
+        <v>304</v>
       </c>
       <c r="J4" s="16" t="s">
-        <v>184</v>
+        <v>305</v>
       </c>
       <c r="K4" s="16" t="s">
         <v>173</v>
@@ -32442,7 +32460,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CF5CE56-EC25-4FB7-A62C-2823D6365594}">
-  <dimension ref="A1:Z1017"/>
+  <dimension ref="A1:Z1019"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.44140625" customWidth="1"/>
@@ -33247,12 +33265,12 @@
       <c r="Y25" s="1"/>
       <c r="Z25" s="1"/>
     </row>
-    <row r="26" spans="1:26" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:26" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>292</v>
+        <v>305</v>
+      </c>
+      <c r="B26" s="166" t="s">
+        <v>307</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
@@ -33279,12 +33297,12 @@
       <c r="Y26" s="1"/>
       <c r="Z26" s="1"/>
     </row>
-    <row r="27" spans="1:26" ht="53.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:26" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
@@ -33311,12 +33329,12 @@
       <c r="Y27" s="1"/>
       <c r="Z27" s="1"/>
     </row>
-    <row r="28" spans="1:26" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:26" ht="53.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="7" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>243</v>
+        <v>293</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
@@ -33343,12 +33361,12 @@
       <c r="Y28" s="1"/>
       <c r="Z28" s="1"/>
     </row>
-    <row r="29" spans="1:26" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:26" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="7" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>210</v>
+        <v>243</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
@@ -33375,12 +33393,12 @@
       <c r="Y29" s="1"/>
       <c r="Z29" s="1"/>
     </row>
-    <row r="30" spans="1:26" ht="93" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:26" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="7" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
@@ -33407,12 +33425,12 @@
       <c r="Y30" s="1"/>
       <c r="Z30" s="1"/>
     </row>
-    <row r="31" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:26" ht="93" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
@@ -33441,10 +33459,10 @@
     </row>
     <row r="32" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="7" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
@@ -33471,12 +33489,12 @@
       <c r="Y32" s="1"/>
       <c r="Z32" s="1"/>
     </row>
-    <row r="33" spans="1:26" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="7" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>223</v>
+        <v>198</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
@@ -33503,12 +33521,12 @@
       <c r="Y33" s="1"/>
       <c r="Z33" s="1"/>
     </row>
-    <row r="34" spans="1:26" ht="66.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:26" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="7" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>294</v>
+        <v>223</v>
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
@@ -33535,12 +33553,12 @@
       <c r="Y34" s="1"/>
       <c r="Z34" s="1"/>
     </row>
-    <row r="35" spans="1:26" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:26" ht="66.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="7" t="s">
-        <v>296</v>
+        <v>193</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
@@ -33567,12 +33585,12 @@
       <c r="Y35" s="1"/>
       <c r="Z35" s="1"/>
     </row>
-    <row r="36" spans="1:26" ht="106.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:26" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="7" t="s">
-        <v>201</v>
+        <v>296</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>212</v>
+        <v>297</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
@@ -33599,12 +33617,12 @@
       <c r="Y36" s="1"/>
       <c r="Z36" s="1"/>
     </row>
-    <row r="37" spans="1:26" ht="66.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:26" ht="106.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="7" t="s">
-        <v>239</v>
+        <v>201</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>240</v>
+        <v>212</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
@@ -33631,11 +33649,13 @@
       <c r="Y37" s="1"/>
       <c r="Z37" s="1"/>
     </row>
-    <row r="38" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="B38" s="2"/>
+    <row r="38" spans="1:26" ht="66.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>240</v>
+      </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
@@ -33661,13 +33681,11 @@
       <c r="Y38" s="1"/>
       <c r="Z38" s="1"/>
     </row>
-    <row r="39" spans="1:26" ht="79.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>209</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="B39" s="2"/>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
@@ -33695,10 +33713,10 @@
     </row>
     <row r="40" spans="1:26" ht="79.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="6" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
@@ -33725,12 +33743,12 @@
       <c r="Y40" s="1"/>
       <c r="Z40" s="1"/>
     </row>
-    <row r="41" spans="1:26" ht="106.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:26" ht="93" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="6" t="s">
-        <v>173</v>
+        <v>304</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>207</v>
+        <v>306</v>
       </c>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
@@ -33757,12 +33775,12 @@
       <c r="Y41" s="1"/>
       <c r="Z41" s="1"/>
     </row>
-    <row r="42" spans="1:26" ht="106.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:26" ht="79.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
@@ -33789,12 +33807,12 @@
       <c r="Y42" s="1"/>
       <c r="Z42" s="1"/>
     </row>
-    <row r="43" spans="1:26" ht="79.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:26" ht="106.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="6" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>244</v>
+        <v>207</v>
       </c>
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
@@ -33821,12 +33839,12 @@
       <c r="Y43" s="1"/>
       <c r="Z43" s="1"/>
     </row>
-    <row r="44" spans="1:26" ht="79.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:26" ht="106.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="6" t="s">
-        <v>194</v>
+        <v>175</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
@@ -33853,12 +33871,12 @@
       <c r="Y44" s="1"/>
       <c r="Z44" s="1"/>
     </row>
-    <row r="45" spans="1:26" ht="145.80000000000001" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:26" ht="79.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>204</v>
+        <v>244</v>
       </c>
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
@@ -33885,12 +33903,12 @@
       <c r="Y45" s="1"/>
       <c r="Z45" s="1"/>
     </row>
-    <row r="46" spans="1:26" ht="66.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:26" ht="79.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="6" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>160</v>
+        <v>205</v>
       </c>
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
@@ -33917,12 +33935,12 @@
       <c r="Y46" s="1"/>
       <c r="Z46" s="1"/>
     </row>
-    <row r="47" spans="1:26" ht="79.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:26" ht="145.80000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="6" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
@@ -33949,12 +33967,12 @@
       <c r="Y47" s="1"/>
       <c r="Z47" s="1"/>
     </row>
-    <row r="48" spans="1:26" ht="119.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:26" ht="66.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="6" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>203</v>
+        <v>160</v>
       </c>
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
@@ -33983,10 +34001,10 @@
     </row>
     <row r="49" spans="1:26" ht="79.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>295</v>
+        <v>195</v>
       </c>
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
@@ -34013,12 +34031,12 @@
       <c r="Y49" s="1"/>
       <c r="Z49" s="1"/>
     </row>
-    <row r="50" spans="1:26" ht="198.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:26" ht="119.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="6" t="s">
-        <v>200</v>
+        <v>181</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>300</v>
+        <v>203</v>
       </c>
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
@@ -34045,12 +34063,12 @@
       <c r="Y50" s="1"/>
       <c r="Z50" s="1"/>
     </row>
-    <row r="51" spans="1:26" ht="119.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:26" ht="79.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="6" t="s">
-        <v>241</v>
+        <v>182</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>242</v>
+        <v>295</v>
       </c>
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
@@ -34077,9 +34095,13 @@
       <c r="Y51" s="1"/>
       <c r="Z51" s="1"/>
     </row>
-    <row r="52" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="1"/>
-      <c r="B52" s="1"/>
+    <row r="52" spans="1:26" ht="198.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>300</v>
+      </c>
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
@@ -34105,9 +34127,13 @@
       <c r="Y52" s="1"/>
       <c r="Z52" s="1"/>
     </row>
-    <row r="53" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="1"/>
-      <c r="B53" s="1"/>
+    <row r="53" spans="1:26" ht="119.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>242</v>
+      </c>
       <c r="C53" s="1"/>
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
@@ -61125,6 +61151,62 @@
       <c r="Y1017" s="1"/>
       <c r="Z1017" s="1"/>
     </row>
+    <row r="1018" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1018" s="1"/>
+      <c r="B1018" s="1"/>
+      <c r="C1018" s="1"/>
+      <c r="D1018" s="1"/>
+      <c r="E1018" s="1"/>
+      <c r="F1018" s="1"/>
+      <c r="G1018" s="1"/>
+      <c r="H1018" s="1"/>
+      <c r="I1018" s="1"/>
+      <c r="J1018" s="1"/>
+      <c r="K1018" s="1"/>
+      <c r="L1018" s="1"/>
+      <c r="M1018" s="1"/>
+      <c r="N1018" s="1"/>
+      <c r="O1018" s="1"/>
+      <c r="P1018" s="1"/>
+      <c r="Q1018" s="1"/>
+      <c r="R1018" s="1"/>
+      <c r="S1018" s="1"/>
+      <c r="T1018" s="1"/>
+      <c r="U1018" s="1"/>
+      <c r="V1018" s="1"/>
+      <c r="W1018" s="1"/>
+      <c r="X1018" s="1"/>
+      <c r="Y1018" s="1"/>
+      <c r="Z1018" s="1"/>
+    </row>
+    <row r="1019" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1019" s="1"/>
+      <c r="B1019" s="1"/>
+      <c r="C1019" s="1"/>
+      <c r="D1019" s="1"/>
+      <c r="E1019" s="1"/>
+      <c r="F1019" s="1"/>
+      <c r="G1019" s="1"/>
+      <c r="H1019" s="1"/>
+      <c r="I1019" s="1"/>
+      <c r="J1019" s="1"/>
+      <c r="K1019" s="1"/>
+      <c r="L1019" s="1"/>
+      <c r="M1019" s="1"/>
+      <c r="N1019" s="1"/>
+      <c r="O1019" s="1"/>
+      <c r="P1019" s="1"/>
+      <c r="Q1019" s="1"/>
+      <c r="R1019" s="1"/>
+      <c r="S1019" s="1"/>
+      <c r="T1019" s="1"/>
+      <c r="U1019" s="1"/>
+      <c r="V1019" s="1"/>
+      <c r="W1019" s="1"/>
+      <c r="X1019" s="1"/>
+      <c r="Y1019" s="1"/>
+      <c r="Z1019" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
